--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По марже" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По марже'!$A$3:$N$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По марже'!$A$3:$O$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -42,7 +42,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -132,19 +137,22 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -512,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -527,8 +535,9 @@
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="70" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -550,6 +559,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -570,6 +580,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -634,10 +645,15 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
+          <t>Пересчитано 27.10</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>Комментарий</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
@@ -648,7 +664,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.599</v>
+        <v>0.633</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
@@ -684,22 +700,27 @@
         <v>77494934.25</v>
       </c>
       <c r="J4" s="8" t="n">
-        <v>31105809</v>
+        <v>28477107</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>28232973</v>
+        <v>20739271</v>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Расчёт по прайсу Техноавиа (розн.-опт, с НДС) даёт себестоимость ~30,6 млн при НМЦК 77,5 млн — разрыв подозрительно большой: проверить в «Приложения_к_Извещению.rar» количество, срок (возможно, поставка на 2–3 года/по за</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: было 60%. Не хватает: ['Приложения_к_Извещению.rar (ТЗ) — недоступен (zakupki.gov.ru и etp.gpb.ru из среды не открываются): требуемый ATPV/ЗЭТВ кал/см² и класс защиты по каждой из 12 позиций, ГОСТ (ГОСТ Р 12.4.234/ ГОСТ 12.4.297, ТР ТС 019/2011), цвета, ростовки', 'Вопрос заказчик</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -756,12 +777,13 @@
           <t>med</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>ТЗ требует завинчивающуюся/поворотную крышку — у МиниМед тип крышки на сайте не указан, подтвердить у производителя до подачи; Требуются насечки на пробирке и крышке — подтвердить; ПП 1875: запрет иностранных — нужен рос</t>
-        </is>
-      </c>
-      <c r="N5" s="9" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr"/>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>ТЗ требует завинчивающуюся/поворотную крышку — у МиниМед тип крышки на сайте не указан, подтвердить у производителя до подачи; Требуются насечки на пробирке и крышке — подтвердить; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -818,12 +840,13 @@
           <t>high</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr"/>
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>полный построчный расчёт и счета поставщиков (KAMCHATKA_STATUS_2610); 163 позиции ещё не котированы</t>
         </is>
       </c>
-      <c r="N6" s="9" t="inlineStr">
+      <c r="O6" s="10" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616346943</t>
         </is>
@@ -834,56 +857,61 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.441</v>
+        <v>0.3891</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Участвовать — при опыте 4,85 млн</t>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>05.11.2026 10:00</t>
+          <t>30.10.2026 12:00</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Арматура/ППУ</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>11202-РЕМ ПРОД-2027-СЭ</t>
+          <t>32616491901</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Сахалинэнерго, лот 2: арматура СиНД для ЮС ТЭЦ-1 (87 поз.)</t>
+          <t>Фасонные изделия и элементы в ППУ изоляции для филиала «Свердловский» ПАО «Т Плюс» (242/27</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
+          <t>ПАО «Т Плюс» (филиал «Свердловский»)</t>
         </is>
       </c>
       <c r="I7" s="8" t="n">
-        <v>16153216.67</v>
-      </c>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="8" t="n"/>
+        <v>8772811.82</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>5359602</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>1582213</v>
+      </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>маржа по 63 из 87 позиций (56% НМЦ); 24 позиции без цены; отборочное требование — опыт ≥ 30% НМЦ (SAKHALIN_11201_11202)</t>
-        </is>
-      </c>
-      <c r="N7" s="9" t="inlineStr">
-        <is>
-          <t>https://rushydro.roseltorg.ru</t>
+      <c r="M7" s="6" t="inlineStr"/>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>Цены за ед. НМЦК нет (только сумма), маржа оценена по себестоимости 73 позиций (2 058 шт). Источник основных цен — прайс СКТК (с НДС, сметные 2021/22 — на отводах совпадают с ПКФ ТЕПЛО 2026, опоры проиндексированы ×1,25), скользящие опоры — ПКФ ТЕПЛО 2026, концевые — ЛТР. Тип 2 (ППУ2) +10% [оценка].</t>
+        </is>
+      </c>
+      <c r="O7" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
         </is>
       </c>
     </row>
@@ -892,60 +920,65 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.3891</v>
+        <v>0.372</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Участвовать</t>
+          <t>Участвовать — при опыте 4,85 млн</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>05.11.2026 10:00</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Арматура/ППУ</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>32616491901</t>
+          <t>11202-РЕМ ПРОД-2027-СЭ</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Фасонные изделия и элементы в ППУ изоляции для филиала «Свердловский» ПАО «Т Плюс» (242/27</t>
+          <t>Сахалинэнерго, лот 2: арматура СиНД для ЮС ТЭЦ-1 (87 поз.)</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Т Плюс» (филиал «Свердловский»)</t>
+          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>8772811.82</v>
+        <v>16153216.67</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>5359602</v>
+        <v>10149833</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>1582213</v>
+        <v>3063717</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>Цены за ед. НМЦК нет (только сумма), маржа оценена по себестоимости 73 позиций (2 058 шт). Источник основных цен — прайс СКТК (с НДС, сметные 2021/22 — на отводах совпадают с ПКФ ТЕПЛО 2026, опоры проиндексированы ×1,25)</t>
-        </is>
-      </c>
-      <c r="N8" s="9" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт ≥ 4,85 млн</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>https://rushydro.roseltorg.ru</t>
         </is>
       </c>
     </row>
@@ -954,16 +987,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.376</v>
+        <v>0.362</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Участвовать</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 10:00</t>
+          <t>30.10.2026 10:00</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -973,39 +1006,40 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>32616489407</t>
+          <t>0848300064126000376</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>МИ №232: спецодежда, спецобувь, СИЗ и дерматологические СИЗ для АО «Уралтурбо»</t>
+          <t>Поставка модуля пневмокаркасного комбинированного</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>АО «Уралтурбо» (организатор ООО «ГЭХ Закупки»)</t>
+          <t>МБУ «Центр по делам ГО и ЧС г.о. Балашиха» (совмес</t>
         </is>
       </c>
       <c r="I9" s="8" t="n">
-        <v>14973624.91</v>
+        <v>1355166.67</v>
       </c>
       <c r="J9" s="8" t="n">
-        <v>9337698</v>
+        <v>865000</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>3165197</v>
-      </c>
-      <c r="L9" s="10" t="inlineStr">
+        <v>268986</v>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>102 позиции, цен за ед. в ЕИС нет (НМЦК делим условно); около 40% себестоимости — оценки без прайса (ПВС-шлемы, дерматология, перчатки). Самые денежные позиции: 25 000 полумасок, ~11 000 пар перчаток, 812 касок. Были раз</t>
-        </is>
-      </c>
-      <c r="N9" s="9" t="inlineStr">
+      <c r="M9" s="6" t="inlineStr"/>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>Себестоимость — оценка без КП. Запрет иностранного (ПП 1875): модуль и, вероятно, агрегат должны быть российскими с записью в ГИСП. Набор характеристик похож на конкретного производителя модулей для МЧС (Номадика, Арктика, ПневмоСибирь и т.п.) — запросить КП у 2–3 фабрик. Срок изготовления 2–4 недел</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1016,7 +1050,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.363</v>
+        <v>0.352</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -1025,7 +1059,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 10:00</t>
+          <t>02.11.2026 10:00</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1035,39 +1069,44 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>32616489910</t>
+          <t>32616489407</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>МИ №308: поставка соли технической для Химкинского филиала ООО «ТСК Мосэнерго»</t>
+          <t>МИ №232: спецодежда, спецобувь, СИЗ и дерматологические СИЗ для АО «Уралтурбо»</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>ООО «Теплоснабжающая компания Мосэнерго» (организа</t>
+          <t>АО «Уралтурбо» (организатор ООО «ГЭХ Закупки»)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n">
-        <v>44596673</v>
+        <v>14973624.91</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>28391015</v>
+        <v>9703399</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>8917768</v>
-      </c>
-      <c r="L10" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>Сколько навала и сколько таблеток — неизвестно (ТЗ в 308_МИ.rar, EIS недоступен): принято 85/15 по деньгам, т.е. ~3 345 т навала и ~197 т таблеток. Если ТЗ на ХВО требует NaCl ≥97–99% / ГОСТ Р 51574, навал дороже (8–11 т</t>
-        </is>
-      </c>
-      <c r="N10" s="9" t="inlineStr">
+        <v>2844132</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: было 38%. Не хватает: ['ТЗ и ценовая форма из 232МИ_кор._от_23.10.zip (zakupki.gov.ru/223/filestore uid=AA9084275251441FB26B2EAABC4DDC40) — нужны марка/класс/объём по каждой позиции; из среды не скачивается (1 попытка, HTTP 000). Запросить у организатора (ssviatova@geh-zakupki.ru)</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1077,8 +1116,8 @@
       <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>0.362</v>
+      <c r="B11" s="12" t="n">
+        <v>0.28</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -1087,49 +1126,50 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 10:00</t>
+          <t>28.10.2026 09:00</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
+          <t>Видеонаблюдение/IT</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>0848300064126000376</t>
+          <t>0318300028426000179</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Поставка модуля пневмокаркасного комбинированного</t>
+          <t>Поставка нейросетевого IP-видеорегистратора TRASSIR для развития АПК «Безопасный город» (Д</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>МБУ «Центр по делам ГО и ЧС г.о. Балашиха» (совмес</t>
+          <t>МКУ МО Динской район «ЕДДС»</t>
         </is>
       </c>
       <c r="I11" s="8" t="n">
-        <v>1355166.67</v>
+        <v>1525990</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>865000</v>
+        <v>1099000</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>268986</v>
-      </c>
-      <c r="L11" s="10" t="inlineStr">
+        <v>193182</v>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Себестоимость — оценка без КП. Запрет иностранного (ПП 1875): модуль и, вероятно, агрегат должны быть российскими с записью в ГИСП. Набор характеристик похож на конкретного производителя модулей для МЧС (Номадика, Арктик</t>
-        </is>
-      </c>
-      <c r="N11" s="9" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr"/>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>Подача 28.10 09:00 МСК — 1,5 суток. Бренд задан (TRASSIR, без эквивалента) — цену даёт только DSSL/дистрибьютор по проекту (нужен ИНН заказчика и адрес, у интегратора «Безопасного города» может быть защита проекта → нам дадут цену хуже). Если лицензии на 160 каналов не требуются — себестоимость ~0,5</t>
+        </is>
+      </c>
+      <c r="O11" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1139,59 +1179,60 @@
       <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="5" t="n">
-        <v>0.334</v>
+      <c r="B12" s="12" t="n">
+        <v>0.256</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Участвовать</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 10:00</t>
+          <t>29.10.2026 09:00</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
+          <t>Пробирки</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>0372200087626000024</t>
+          <t>0372100001026000499</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Поставка кадетской формы в 2026 году</t>
+          <t>Поставка медицинских изделий (пробирок вакуумных) на 2027 год</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>ГБОУ Школа № 380 Красносельского р-на СПб им. А.И.</t>
+          <t>Федеральное ГБУЗ СПБ клиническая больница Российск</t>
         </is>
       </c>
       <c r="I12" s="8" t="n">
-        <v>2490692</v>
+        <v>1500000</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>1659080</v>
+        <v>1116048</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>433555</v>
+        <v>95251</v>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>Запрет иностранного (ПП 1875) по обуви и одежде: нужна запись в реестре ГИСП/ЕАЭС на каждую позицию. Ботинки названы «Зубр» — проверить, что допускается эквивалент. Размерная сетка по согласованию — пошив/подбор по разме</t>
-        </is>
-      </c>
-      <c r="N12" s="9" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr"/>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Контракт с неопределённым объёмом (quantityUndefined): цены за ед. (сумма ед. цен 123,84 ₽), поставка по заявкам в 2027 г. до исчерпания 1,5 млн. Доли позиций неизвестны — для расчёта приняты равные доли стоимости.; нет подтверждённого российского аналога (запрет ПП 1875); Упаковка «в штативе из неп</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1201,17 +1242,17 @@
       <c r="A13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="11" t="n">
-        <v>0.28</v>
+      <c r="B13" s="12" t="n">
+        <v>0.234</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 09:00</t>
+          <t>30.10.2026 07:00</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1221,39 +1262,40 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>0318300028426000179</t>
+          <t>0137100001526000235</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Поставка нейросетевого IP-видеорегистратора TRASSIR для развития АПК «Безопасный город» (Д</t>
+          <t>Поставка терминалов зарядки, архивирования и хранения данных для персональных видеорегистр</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>МКУ МО Динской район «ЕДДС»</t>
+          <t>Приокский тыловой таможенный пост (ФТС)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n">
-        <v>1525990</v>
+        <v>4350000</v>
       </c>
       <c r="J13" s="8" t="n">
-        <v>1099000</v>
+        <v>3330000</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>193182</v>
-      </c>
-      <c r="L13" s="10" t="inlineStr">
+        <v>377570</v>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Подача 28.10 09:00 МСК — 1,5 суток. Бренд задан (TRASSIR, без эквивалента) — цену даёт только DSSL/дистрибьютор по проекту (нужен ИНН заказчика и адрес, у интегратора «Безопасного города» может быть защита проекта → нам </t>
-        </is>
-      </c>
-      <c r="N13" s="9" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr"/>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>Цена 1,45 млн/шт в 4 раза выше типовых 20-слотовых терминалов → вероятна привязка к конкретной экосистеме (ПО/регистраторы, которые уже есть у таможни), поставку контролирует производитель/дилер. ПП 1875: ограничение (isRestrictForeignPurchaseObjects=true) — нужен товар из реестра российской РЭП (ГИ</t>
+        </is>
+      </c>
+      <c r="O13" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1263,8 +1305,8 @@
       <c r="A14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="11" t="n">
-        <v>0.256</v>
+      <c r="B14" s="12" t="n">
+        <v>0.227</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1273,49 +1315,54 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>29.10.2026 09:00</t>
+          <t>28.10.2026 10:00</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Пробирки</t>
+          <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>0372100001026000499</t>
+          <t>32616489910</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Поставка медицинских изделий (пробирок вакуумных) на 2027 год</t>
+          <t>МИ №308: поставка соли технической для Химкинского филиала ООО «ТСК Мосэнерго»</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Федеральное ГБУЗ СПБ клиническая больница Российск</t>
+          <t>ООО «Теплоснабжающая компания Мосэнерго» (организа</t>
         </is>
       </c>
       <c r="I14" s="8" t="n">
-        <v>1500000</v>
+        <v>44596673</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>1116048</v>
+        <v>34471162</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>95251</v>
+        <v>3579732</v>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Контракт с неопределённым объёмом (quantityUndefined): цены за ед. (сумма ед. цен 123,84 ₽), поставка по заявкам в 2027 г. до исчерпания 1,5 млн. Доли позиций неизвестны — для расчёта приняты равные доли стоимости.; нет </t>
-        </is>
-      </c>
-      <c r="N14" s="9" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПЕРЕСЧИТАНО 27.10: было 36%. Не хватает: ['308_МИ.rar (ТЗ) — недоступен (zakupki.gov.ru/etp.gpb.ru не отвечают): тоннаж навала и таблеток по годам, ГОСТ/тип (ГОСТ Р 51574 / ГОСТ 13830, тип/сорт, NaCl ≥97–99%, антислеживатель), точки поставки (одна котельная/ТЭЦ или несколько), способ (ж/д или авто, </t>
+        </is>
+      </c>
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1325,59 +1372,60 @@
       <c r="A15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>0.234</v>
+      <c r="B15" s="12" t="n">
+        <v>0.2143</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 07:00</t>
+          <t>02.11.2026 12:00</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Видеонаблюдение/IT</t>
+          <t>Арматура/ППУ</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>0137100001526000235</t>
+          <t>32616495280</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Поставка терминалов зарядки, архивирования и хранения данных для персональных видеорегистр</t>
+          <t>Фасонные изделия и элементы в ППУ изоляции для нужд АО «ЕТК» (244/27, 4651032)</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Приокский тыловой таможенный пост (ФТС)</t>
+          <t>АО «Екатеринбургская Теплосетевая Компания»</t>
         </is>
       </c>
       <c r="I15" s="8" t="n">
-        <v>4350000</v>
+        <v>46388455.4</v>
       </c>
       <c r="J15" s="8" t="n">
-        <v>3330000</v>
+        <v>36449290</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>377570</v>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
+        <v>1247054</v>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>Цена 1,45 млн/шт в 4 раза выше типовых 20-слотовых терминалов → вероятна привязка к конкретной экосистеме (ПО/регистраторы, которые уже есть у таможни), поставку контролирует производитель/дилер. ПП 1875: ограничение (is</t>
-        </is>
-      </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="M15" s="6" t="inlineStr"/>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>Цены за ед. НМЦК нет. 60% себестоимости — Ду 720–1020 (отводы 820х11 ×26, опоры 720 ×34, опоры 820/1020 со щитами): цены на них в открытых прайсах только у Сайверхот (розница: 720х8 165 тыс., 820х9 346 тыс.) — пересчитаны ×1,1 стенка ×0,85 [оценка]; неподвижные опоры 720–1020 — экстраполяция [оценка</t>
+        </is>
+      </c>
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1387,57 +1435,62 @@
       <c r="A16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="n">
-        <v>0.23</v>
+      <c r="B16" s="12" t="n">
+        <v>0.21</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Осторожно — при опыте 3,68 млн</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>05.11.2026 10:00</t>
+          <t>29.10.2026 09:30</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>11201-РЕМ ПРОД-2027-СЭ</t>
+          <t>0327300018526000001</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Сахалинэнерго, лот 1: арматура СиНД для Сахалинской ГРЭС (83 поз.)</t>
+          <t>Поставка хоккейной экипировки</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
+          <t>МБУ «ФОК» г. Новозыбкова (описание объекта — МБУДО</t>
         </is>
       </c>
       <c r="I16" s="8" t="n">
-        <v>12269140</v>
-      </c>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>маржа по 54 из 83 позиций (47% НМЦ); затворы п.19–20 убыточны; опыт ≥ 30% НМЦ</t>
-        </is>
-      </c>
-      <c r="N16" s="9" t="inlineStr">
-        <is>
-          <t>https://rushydro.roseltorg.ru</t>
+        <v>2999795.9</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>2369841</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>195895</v>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>50 позиций, в основном импортные бренды. В закупке действует ограничение для иностранных товаров (isRestrictForeignPurchaseObjects): при одной заявке с российским товаром импортные отклоняются, а российских производителей экипировки мало. Маржа тонкая (≈20% до торга): НМЦК собран по рознице. Нужен п</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
         </is>
       </c>
     </row>
@@ -1445,8 +1498,8 @@
       <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="n">
-        <v>0.2143</v>
+      <c r="B17" s="12" t="n">
+        <v>0.2081</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
@@ -1455,7 +1508,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 12:00</t>
+          <t>05.11.2026 12:00</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1465,39 +1518,40 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>32616495280</t>
+          <t>32616501405</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Фасонные изделия и элементы в ППУ изоляции для нужд АО «ЕТК» (244/27, 4651032)</t>
+          <t>Поставка труб ПЭ100 и ПП, фитингов в ассортименте</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>АО «Екатеринбургская Теплосетевая Компания»</t>
+          <t>ООО «СМЭУ «Заневка»</t>
         </is>
       </c>
       <c r="I17" s="8" t="n">
-        <v>46388455.4</v>
+        <v>7019054.69</v>
       </c>
       <c r="J17" s="8" t="n">
-        <v>36449290</v>
+        <v>5558195</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>1247054</v>
-      </c>
-      <c r="L17" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>Цены за ед. НМЦК нет. 60% себестоимости — Ду 720–1020 (отводы 820х11 ×26, опоры 720 ×34, опоры 820/1020 со щитами): цены на них в открытых прайсах только у Сайверхот (розница: 720х8 165 тыс., 820х9 346 тыс.) — пересчитан</t>
-        </is>
-      </c>
-      <c r="N17" s="9" t="inlineStr">
+        <v>446830</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>87% суммы — труба 225 мм (2 990 м по 2 044 ₽). SDR в ЕИС не указан (ТЗ в Прил.1 — zakupki.gov.ru недоступен): при SDR17 маржа ок, при SDR11 (2 278 ₽/м) себестоимость 7.63 млн ≈ НМЦК → убыток. Втулка 225 по рынку 1 331 &gt; НМЦК 990. Нацрежим: ограничение (ПП 1875) по ПЭ-позициям — нужен российский прои</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1507,17 +1561,17 @@
       <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="11" t="n">
-        <v>0.21</v>
+      <c r="B18" s="12" t="n">
+        <v>0.2</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>29.10.2026 09:30</t>
+          <t>28.10.2026 11:00</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1527,112 +1581,106 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>0327300018526000001</t>
+          <t>B2010261157408</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>Поставка хоккейной экипировки</t>
+          <t>Поставка армейских палаток для филиалов АНО ДПО «ВОИН» (Амурская обл., ЕАО, Карелия, Примо</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>МБУ «ФОК» г. Новозыбкова (описание объекта — МБУДО</t>
+          <t>АНО ДПО «Центр развития военно-спортивной подготов</t>
         </is>
       </c>
       <c r="I18" s="8" t="n">
-        <v>2999795.9</v>
+        <v>2210933.36</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>2369841</v>
+        <v>1768747</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>195895</v>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
+        <v>124970</v>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>50 позиций, в основном импортные бренды. В закупке действует ограничение для иностранных товаров (isRestrictForeignPurchaseObjects): при одной заявке с российским товаром импортные отклоняются, а российских производителе</t>
-        </is>
-      </c>
-      <c r="N18" s="9" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
+      <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>Спецификация недоступна, модель и количество неизвестны. Доставка в 4 удалённых точки (Петрозаводск, Благовещенск, Владивосток, Хабаровск) — дорогая логистика, около 5% [оценка]. До подачи меньше 2 суток (28.10 11:00). Подавать, только если сегодня-завтра получим ТЗ и КП фабрики (ПК «Агролиз», Пневм</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="11" t="n">
-        <v>0.2081</v>
+      <c r="B19" s="13" t="n">
+        <v>0.1966</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>05.11.2026 12:00</t>
+          <t>30.10.2026 10:00</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Арматура/ППУ</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>32616501405</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Поставка труб ПЭ100 и ПП, фитингов в ассортименте</t>
+          <t>Поставка арматуры трубопроводной</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>ООО «СМЭУ «Заневка»</t>
+          <t>ООО «Ремонтно-механический завод» (Салават)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n">
-        <v>7019054.69</v>
+        <v>18813618</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>5558195</v>
+        <v>15114861</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>446830</v>
-      </c>
-      <c r="L19" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M19" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87% суммы — труба 225 мм (2 990 м по 2 044 ₽). SDR в ЕИС не указан (ТЗ в Прил.1 — zakupki.gov.ru недоступен): при SDR17 маржа ок, при SDR11 (2 278 ₽/м) себестоимость 7.63 млн ≈ НМЦК → убыток. Втулка 225 по рынку 1 331 &gt; </t>
-        </is>
-      </c>
-      <c r="N19" s="9" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
+        <v>1007259</v>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="11" t="n">
-        <v>0.2</v>
+      <c r="B20" s="13" t="n">
+        <v>0.1966</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -1641,55 +1689,56 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 11:00</t>
+          <t>28.10.2026 13:00</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>B2010261157408</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Поставка армейских палаток для филиалов АНО ДПО «ВОИН» (Амурская обл., ЕАО, Карелия, Примо</t>
+          <t>Затвор дисковый (56-100)</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>АНО ДПО «Центр развития военно-спортивной подготов</t>
+          <t>ООО «Ремонтно-механический завод» (Салават)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n">
-        <v>2210933.36</v>
+        <v>10474222</v>
       </c>
       <c r="J20" s="8" t="n">
-        <v>1768747</v>
+        <v>8414990</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>124970</v>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
+        <v>560778</v>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr">
-        <is>
-          <t>Спецификация недоступна, модель и количество неизвестны. Доставка в 4 удалённых точки (Петрозаводск, Благовещенск, Владивосток, Хабаровск) — дорогая логистика, около 5% [оценка]. До подачи меньше 2 суток (28.10 11:00). П</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="13" t="n">
         <v>0.1966</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1699,7 +1748,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 10:00</t>
+          <t>02.11.2026 13:00</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1709,12 +1758,12 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Поставка арматуры трубопроводной</t>
+          <t>Поставка затворов</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -1723,31 +1772,32 @@
         </is>
       </c>
       <c r="I21" s="8" t="n">
-        <v>18813618</v>
+        <v>5271798.95</v>
       </c>
       <c r="J21" s="8" t="n">
-        <v>15114861</v>
+        <v>4235363</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>1007259</v>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
+        <v>282246</v>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M21" s="6" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="13" t="n">
         <v>0.1966</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1767,12 +1817,12 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>8004</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Затвор дисковый (56-100)</t>
+          <t>Запорная арматура</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1781,31 +1831,32 @@
         </is>
       </c>
       <c r="I22" s="8" t="n">
-        <v>10474222</v>
+        <v>4248523</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>8414990</v>
+        <v>3413263</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>560778</v>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
+        <v>227461</v>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл</t>
-        </is>
-      </c>
-      <c r="N22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="13" t="n">
         <v>0.1966</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1815,7 +1866,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 13:00</t>
+          <t>28.10.2026 12:00</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1825,55 +1876,56 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>ГП646025</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Поставка затворов</t>
+          <t>Закупка ЗРА и КОФ (890)</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>ООО «Ремонтно-механический завод» (Салават)</t>
+          <t>ООО «НПП «Нефтехимия» (Москва, ИНН 7723332561)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n">
-        <v>5271798.95</v>
+        <v>2000000</v>
       </c>
       <c r="J23" s="8" t="n">
-        <v>4235363</v>
+        <v>1606800</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>282246</v>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
+        <v>107078</v>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M23" s="6" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл</t>
-        </is>
-      </c>
-      <c r="N23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>НПП «Нефтехимия» — производство полипропилена на площадке МНПЗ (Капотня), нефтехим: вероятны 09Г2С/нерж., класс А, ТР ТС 032 (опасные среды), возможна проверка поставщика службой безопасности. Срок 28.10 12:00 — 2 дня, нужен быстрый КП завода. Состав позиций неизвестен.</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="12" t="n">
-        <v>0.1966</v>
+      <c r="B24" s="13" t="n">
+        <v>0.1965</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 13:00</t>
+          <t>28.10.2026 10:00</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1883,55 +1935,60 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>32616480814</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Запорная арматура</t>
+          <t>Поставка запорной арматуры (задвижки 30с41нж/30с941нж Ду50–200, 70 шт)</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>ООО «Ремонтно-механический завод» (Салават)</t>
+          <t>АО «Петербургский Нефтяной Терминал» (ИНН 78050580</t>
         </is>
       </c>
       <c r="I24" s="8" t="n">
-        <v>4248523</v>
+        <v>3163250.24</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>3413263</v>
+        <v>2541597</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>227461</v>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M24" s="6" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл</t>
-        </is>
-      </c>
-      <c r="N24" s="6" t="inlineStr"/>
+        <v>169144</v>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr"/>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>Позиции из ЕИС (8 строк, 70 шт). Ред.3 от 22.10: изменена марка стали в ТЗ (новая ТЗ не скачана — zakupki.gov.ru недоступен) → расчёт консервативно на 09Г2С (30лс41нж), себестоимость ≈2.50 млн. Если сталь 20Л/25Л (обычные 30с41нж) — себестоимость ≈1.28 млн, маржа ~55%. Если 30с941нж — с электроприво</t>
+        </is>
+      </c>
+      <c r="O24" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="12" t="n">
-        <v>0.1966</v>
+      <c r="B25" s="13" t="n">
+        <v>0.1888</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 12:00</t>
+          <t>03.11.2026 08:00</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1941,97 +1998,99 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>ГП646025</t>
+          <t>1029143</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Закупка ЗРА и КОФ (890)</t>
+          <t>Затворы дисковые поворотные 2027</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>ООО «НПП «Нефтехимия» (Москва, ИНН 7723332561)</t>
+          <t>Филиал «Пензенский» ПАО «Т Плюс» (Пенза, Ново-Черк</t>
         </is>
       </c>
       <c r="I25" s="8" t="n">
-        <v>2000000</v>
+        <v>303969.42</v>
       </c>
       <c r="J25" s="8" t="n">
-        <v>1606800</v>
+        <v>246580</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>107078</v>
-      </c>
-      <c r="L25" s="10" t="inlineStr">
+        <v>14193</v>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr">
-        <is>
-          <t>НПП «Нефтехимия» — производство полипропилена на площадке МНПЗ (Капотня), нефтехим: вероятны 09Г2С/нерж., класс А, ТР ТС 032 (опасные среды), возможна проверка поставщика службой безопасности. Срок 28.10 12:00 — 2 дня, н</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>Малый лот (0,3 млн), поставка в 2027. Т Плюс — запрос цен на ЭТП ГПБ, обычно требует регистрации в реестре поставщиков Т Плюс и цены «без НДС/с НДС» — у нас без НДС (сравнение может быть без НДС → потеря ~18% конкурентности). Доставка Пенза — небольшая. Чистая прибыль ~25 тыс. — участвовать только е</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="12" t="n">
-        <v>0.1965</v>
+      <c r="B26" s="13" t="n">
+        <v>0.188</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Участвовать</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 10:00</t>
+          <t>30.10.2026 07:00</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Пробирки</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>32616480814</t>
+          <t>0860200000826008623</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>Поставка запорной арматуры (задвижки 30с41нж/30с941нж Ду50–200, 70 шт)</t>
+          <t>Поставка пробирок</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>АО «Петербургский Нефтяной Терминал» (ИНН 78050580</t>
+          <t>ГУЧ Здравоохранения «Саратовская Городская Поликли</t>
         </is>
       </c>
       <c r="I26" s="8" t="n">
-        <v>3163250.24</v>
+        <v>126000</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>2541597</v>
+        <v>102340</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>169144</v>
+        <v>5770</v>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr">
-        <is>
-          <t>Позиции из ЕИС (8 строк, 70 шт). Ред.3 от 22.10: изменена марка стали в ТЗ (новая ТЗ не скачана — zakupki.gov.ru недоступен) → расчёт консервативно на 09Г2С (30лс41нж), себестоимость ≈2.50 млн. Если сталь 20Л/25Л (обычны</t>
-        </is>
-      </c>
-      <c r="N26" s="9" t="inlineStr">
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr"/>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2041,8 +2100,8 @@
       <c r="A27" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="12" t="n">
-        <v>0.1888</v>
+      <c r="B27" s="13" t="n">
+        <v>0.179</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2051,169 +2110,172 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>03.11.2026 08:00</t>
+          <t>03.11.2026 09:00</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>1029143</t>
+          <t>32616497619</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>Затворы дисковые поворотные 2027</t>
+          <t>Поставка спецодежды, спецобуви и средств индивидуальной и коллективной защиты</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>Филиал «Пензенский» ПАО «Т Плюс» (Пенза, Ново-Черк</t>
+          <t>МУП «Водоканал» г. Белорецк</t>
         </is>
       </c>
       <c r="I27" s="8" t="n">
-        <v>303969.42</v>
+        <v>1264480.67</v>
       </c>
       <c r="J27" s="8" t="n">
-        <v>246580</v>
+        <v>1038520</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>14193</v>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>Малый лот (0,3 млн), поставка в 2027. Т Плюс — запрос цен на ЭТП ГПБ, обычно требует регистрации в реестре поставщиков Т Плюс и цены «без НДС/с НДС» — у нас без НДС (сравнение может быть без НДС → потеря ~18% конкурентно</t>
-        </is>
-      </c>
-      <c r="N27" s="6" t="inlineStr"/>
+        <v>26501</v>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr"/>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тонко: безубыточное снижение ~14,5%, при снижении 12% net ~26 тыс. Подавать с ценой не ниже −5…−8% от НМЦК. Конкурс: кроме цены оцениваются критерии (опыт, квалификация — «Таблица оценочных критериев.xlsx»), без опыта шансы ниже. 82% себестоимости — зимние костюмы по правилу клиента 5 000 ₽; если в </t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="n">
-        <v>0.188</v>
+      <c r="B28" s="13" t="n">
+        <v>0.177</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 07:00</t>
+          <t>30.10.2026 15:00</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Пробирки</t>
+          <t>Видеонаблюдение/IT</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>0860200000826008623</t>
+          <t>SBR063-260750911700213</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Поставка пробирок</t>
+          <t>7714-OD Приобретение видеорегистраторов для системы видеонаблюдения КТК-Р</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>ГУЧ Здравоохранения «Саратовская Городская Поликли</t>
+          <t>АО «Каспийский Трубопроводный Консорциум-Р»</t>
         </is>
       </c>
       <c r="I28" s="8" t="n">
-        <v>126000</v>
+        <v>30287213.11</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>102340</v>
+        <v>24925515</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>5770</v>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M28" s="6" t="inlineStr">
-        <is>
-          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
-        </is>
-      </c>
-      <c r="N28" s="9" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
+        <v>1101124</v>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr"/>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>Позиции/бренды неизвестны (КТК часто задаёт конкретные бренды и номенклатуру по проекту, двуязычная документация, квалификация/проверка контрагента КТК, опыт аналогичных поставок). 30 млн — большой оборотный капитал на 60+ дней; вероятно оплата по факту поставки. ПП 1875 к КТК-Р формально не применя</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B29" s="12" t="n">
-        <v>0.179</v>
+      <c r="B29" s="13" t="n">
+        <v>0.176</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>03.11.2026 09:00</t>
+          <t>02.11.2026 10:30</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
+          <t>Видеонаблюдение/IT</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>32616497619</t>
+          <t>32616501691</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Поставка спецодежды, спецобуви и средств индивидуальной и коллективной защиты</t>
+          <t>Поставка оборудования и комплектующих для системы мониторинга ЕИСБ для нужд филиала ПАО «Р</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>МУП «Водоканал» г. Белорецк</t>
+          <t>ПАО «Россети Центр и Приволжье»</t>
         </is>
       </c>
       <c r="I29" s="8" t="n">
-        <v>1264480.67</v>
+        <v>3588800.8</v>
       </c>
       <c r="J29" s="8" t="n">
-        <v>1038520</v>
+        <v>2957500</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>26501</v>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>Тонко: безубыточное снижение ~14,5%, при снижении 12% net ~26 тыс. Подавать с ценой не ниже −5…−8% от НМЦК. Конкурс: кроме цены оцениваются критерии (опыт, квалификация — «Таблица оценочных критериев.xlsx»), без опыта ша</t>
-        </is>
-      </c>
-      <c r="N29" s="9" t="inlineStr">
+        <v>126946</v>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr"/>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>Спецификация в RAR на ЕИС (недоступен) — модели/характеристики неизвестны, nmck_unit распределены пропорционально оценочным ценам. ПП 1875 ограничение по 10 из 15 позиций (регистраторы, HDD, мониторы, камеры, ВКС, телеком) — нужны товары из реестра РЭП; HDD российского производства в реестре практич</t>
+        </is>
+      </c>
+      <c r="O29" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2223,75 +2285,76 @@
       <c r="A30" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="12" t="n">
-        <v>0.177</v>
+      <c r="B30" s="13" t="n">
+        <v>0.175</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 15:00</t>
+          <t>30.10.2026 12:00</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Видеонаблюдение/IT</t>
+          <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>SBR063-260750911700213</t>
+          <t>B1510261835045</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>7714-OD Приобретение видеорегистраторов для системы видеонаблюдения КТК-Р</t>
+          <t>Таврида.Арт: форменная одежда службы безопасности</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>АО «Каспийский Трубопроводный Консорциум-Р»</t>
+          <t>АНО «Таврида.Арт»</t>
         </is>
       </c>
       <c r="I30" s="8" t="n">
-        <v>30287213.11</v>
+        <v>4169750</v>
       </c>
       <c r="J30" s="8" t="n">
-        <v>24925515</v>
+        <v>3440900</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>1101124</v>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>Позиции/бренды неизвестны (КТК часто задаёт конкретные бренды и номенклатуру по проекту, двуязычная документация, квалификация/проверка контрагента КТК, опыт аналогичных поставок). 30 млн — большой оборотный капитал на 6</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="inlineStr"/>
+        <v>319215</v>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr"/>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>построчно сверено (TAVRIDA_FINAL_2010); идти при подтверждённом наличии</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B31" s="12" t="n">
-        <v>0.176</v>
+      <c r="B31" s="13" t="n">
+        <v>0.161</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 10:30</t>
+          <t>03.11.2026 07:00</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -2301,39 +2364,40 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>32616501691</t>
+          <t>0829500001126007015</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>Поставка оборудования и комплектующих для системы мониторинга ЕИСБ для нужд филиала ПАО «Р</t>
+          <t>Поставка оборудования для организации видеонаблюдения</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Россети Центр и Приволжье»</t>
+          <t>ГБУЗ «Клиническая станция скорой медицинской помощ</t>
         </is>
       </c>
       <c r="I31" s="8" t="n">
-        <v>3588800.8</v>
+        <v>2081541.45</v>
       </c>
       <c r="J31" s="8" t="n">
-        <v>2957500</v>
+        <v>1747300</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>126946</v>
-      </c>
-      <c r="L31" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>Спецификация в RAR на ЕИС (недоступен) — модели/характеристики неизвестны, nmck_unit распределены пропорционально оценочным ценам. ПП 1875 ограничение по 10 из 15 позиций (регистраторы, HDD, мониторы, камеры, ВКС, телеко</t>
-        </is>
-      </c>
-      <c r="N31" s="9" t="inlineStr">
+        <v>45607</v>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr"/>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>Маржа тонкая (~12%). ПП 1875 ОГРАНИЧЕНИЕ по камерам, коммутаторам, кабелю, NVR и HDD: если хотя бы один участник даст реестровый товар — наша заявка с иностранным (HiWatch/Dahua) будет отклонена; реестровые камеры/коммутаторы (TRASSIR) дороже НМЦК. Кабель — есть российские производители (выгодно бра</t>
+        </is>
+      </c>
+      <c r="O31" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2343,75 +2407,84 @@
       <c r="A32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="12" t="n">
-        <v>0.175</v>
+      <c r="B32" s="13" t="n">
+        <v>0.144</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Осторожно — только после КП АРМАТЭК</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>05.11.2026 10:00</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>B1510261835045</t>
+          <t>11201-РЕМ ПРОД-2027-СЭ</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Таврида.Арт: форменная одежда службы безопасности</t>
+          <t>Сахалинэнерго, лот 1: арматура СиНД для Сахалинской ГРЭС (83 поз.)</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>АНО «Таврида.Арт»</t>
+          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n">
-        <v>4169750</v>
+        <v>12269140</v>
       </c>
       <c r="J32" s="8" t="n">
-        <v>3440900</v>
+        <v>10507218</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>319215</v>
+        <v>-354638</v>
       </c>
       <c r="L32" s="6" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M32" s="6" t="inlineStr">
-        <is>
-          <t>построчно сверено (TAVRIDA_FINAL_2010); идти при подтверждённом наличии</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="inlineStr"/>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: все 83 позиции + доставка; 39% НМЦ — оценка (затворы АРМАТЭК АМ 2,4 млн — цены нет); 16 убыточных строк; при снижении &gt;7% — минус</t>
+        </is>
+      </c>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>https://rushydro.roseltorg.ru</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="12" t="n">
-        <v>0.161</v>
+      <c r="B33" s="13" t="n">
+        <v>0.124</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>03.11.2026 07:00</t>
+          <t>09.11.2026 09:00</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2421,39 +2494,40 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>0829500001126007015</t>
+          <t>32616494964</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>Поставка оборудования для организации видеонаблюдения</t>
+          <t>Поставка вычислительной техники, оргтехники и офисного оборудования</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>ГБУЗ «Клиническая станция скорой медицинской помощ</t>
+          <t>АО «Охинская ТЭЦ»</t>
         </is>
       </c>
       <c r="I33" s="8" t="n">
-        <v>2081541.45</v>
+        <v>2900149.68</v>
       </c>
       <c r="J33" s="8" t="n">
-        <v>1747300</v>
+        <v>2540000</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>45607</v>
-      </c>
-      <c r="L33" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr">
-        <is>
-          <t>Маржа тонкая (~12%). ПП 1875 ОГРАНИЧЕНИЕ по камерам, коммутаторам, кабелю, NVR и HDD: если хотя бы один участник даст реестровый товар — наша заявка с иностранным (HiWatch/Dahua) будет отклонена; реестровые камеры/коммут</t>
-        </is>
-      </c>
-      <c r="N33" s="9" t="inlineStr">
+        <v>-34253</v>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr"/>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>ТЗ и форма КП есть на ЕИС (docx/xlsx), но не скачаны — модели/конфигурации ПК неизвестны; оценка состава 2,45 млн против НМЦК 2,9 млн. Доставка в Оху (север Сахалина) — дорогая и долгая логистика (~3% НМЦК). ПП 1875 ограничение по 7 из 8 позиций — ПК, мониторы, принтеры, регистраторы нужны из реестр</t>
+        </is>
+      </c>
+      <c r="O33" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2463,59 +2537,60 @@
       <c r="A34" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="12" t="n">
-        <v>0.124</v>
+      <c r="B34" s="14" t="n">
+        <v>0.09699999999999999</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>09.11.2026 09:00</t>
+          <t>28.10.2026 05:00</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Видеонаблюдение/IT</t>
+          <t>Пробирки</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>32616494964</t>
+          <t>0334200012526000832</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Поставка вычислительной техники, оргтехники и офисного оборудования</t>
+          <t>Поставка пробирок</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>АО «Охинская ТЭЦ»</t>
+          <t>ГБУЗ Иркутская ордена «Знак Почета» областная клин</t>
         </is>
       </c>
       <c r="I34" s="8" t="n">
-        <v>2900149.68</v>
+        <v>253140</v>
       </c>
       <c r="J34" s="8" t="n">
-        <v>2540000</v>
+        <v>228620</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>-34253</v>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr">
-        <is>
-          <t>ТЗ и форма КП есть на ЕИС (docx/xlsx), но не скачаны — модели/конфигурации ПК неизвестны; оценка состава 2,45 млн против НМЦК 2,9 млн. Доставка в Оху (север Сахалина) — дорогая и долгая логистика (~3% НМЦК). ПП 1875 огра</t>
-        </is>
-      </c>
-      <c r="N34" s="9" t="inlineStr">
+        <v>2059</v>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr"/>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="O34" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2525,8 +2600,8 @@
       <c r="A35" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B35" s="13" t="n">
-        <v>0.09699999999999999</v>
+      <c r="B35" s="14" t="n">
+        <v>0.08800000000000001</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2535,7 +2610,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 05:00</t>
+          <t>01.11.2026 17:00</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -2545,39 +2620,40 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>0334200012526000832</t>
+          <t>0322200005226000562</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Поставка пробирок</t>
+          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД, с активатором свертывания</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>ГБУЗ Иркутская ордена «Знак Почета» областная клин</t>
+          <t xml:space="preserve">Краевое ГБУЗ «Краевая Клиническая Психиатрическая </t>
         </is>
       </c>
       <c r="I35" s="8" t="n">
-        <v>253140</v>
+        <v>422090</v>
       </c>
       <c r="J35" s="8" t="n">
-        <v>228620</v>
+        <v>385000</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>2059</v>
+        <v>102</v>
       </c>
       <c r="L35" s="6" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
-        </is>
-      </c>
-      <c r="N35" s="9" t="inlineStr">
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr"/>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>13 мм на 9–9,5 мл не выпускается (МиниМед 13×100 макс. 7 мл; 9 мл — только 16×100) — характеристика неисполнима, нужен запрос разъяснений; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="O35" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2587,8 +2663,8 @@
       <c r="A36" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="13" t="n">
-        <v>0.08800000000000001</v>
+      <c r="B36" s="14" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2607,12 +2683,12 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>0322200005226000562</t>
+          <t>0322200005226000561</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД, с активатором свертывания</t>
+          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -2621,25 +2697,26 @@
         </is>
       </c>
       <c r="I36" s="8" t="n">
-        <v>422090</v>
+        <v>484797</v>
       </c>
       <c r="J36" s="8" t="n">
-        <v>385000</v>
+        <v>442680</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>102</v>
+        <v>-361</v>
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 мм на 9–9,5 мл не выпускается (МиниМед 13×100 макс. 7 мл; 9 мл — только 16×100) — характеристика неисполнима, нужен запрос разъяснений; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись </t>
-        </is>
-      </c>
-      <c r="N36" s="9" t="inlineStr">
+      <c r="M36" s="6" t="inlineStr"/>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>Убыточные строки (себес &gt; НМЦК ед.): с натрия цитратом [Концентрация цитрата натрия=3.8, D=13, H=; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="O36" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2649,8 +2726,8 @@
       <c r="A37" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="13" t="n">
-        <v>0.08699999999999999</v>
+      <c r="B37" s="14" t="n">
+        <v>0.064</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -2659,7 +2736,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>01.11.2026 17:00</t>
+          <t>29.10.2026 07:00</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2669,39 +2746,40 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>0322200005226000561</t>
+          <t>32616494976</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД</t>
+          <t>Поставка изделий медицинского назначения (пробирки вакуумные)</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Краевое ГБУЗ «Краевая Клиническая Психиатрическая </t>
+          <t>Государственное автономное учреждение Здравоохране</t>
         </is>
       </c>
       <c r="I37" s="8" t="n">
-        <v>484797</v>
+        <v>390420</v>
       </c>
       <c r="J37" s="8" t="n">
-        <v>442680</v>
+        <v>365420</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>-361</v>
-      </c>
-      <c r="L37" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>Убыточные строки (себес &gt; НМЦК ед.): с натрия цитратом [Концентрация цитрата натрия=3.8, D=13, H=; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
-        </is>
-      </c>
-      <c r="N37" s="9" t="inlineStr">
+        <v>-9502</v>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr"/>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>Характеристики (объём, размер, гель или без) в ТЗ закрыты (Извещение.zip, часть_II_измененная.docx — zakupki.gov.ru недоступен); среднее НМЦК 13,70 ₽/шт при 15 000 шт «активатор/гель» — если гель, маржа тонкая; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/Г</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2711,8 +2789,8 @@
       <c r="A38" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="13" t="n">
-        <v>0.064</v>
+      <c r="B38" s="14" t="n">
+        <v>0.038</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -2721,83 +2799,88 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>29.10.2026 07:00</t>
+          <t>02.11.2026 10:00</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Пробирки</t>
+          <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>32616494976</t>
+          <t>0372200087626000024</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>Поставка изделий медицинского назначения (пробирки вакуумные)</t>
+          <t>Поставка кадетской формы в 2026 году</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Государственное автономное учреждение Здравоохране</t>
+          <t>ГБОУ Школа № 380 Красносельского р-на СПб им. А.И.</t>
         </is>
       </c>
       <c r="I38" s="8" t="n">
-        <v>390420</v>
+        <v>2490692</v>
       </c>
       <c r="J38" s="8" t="n">
-        <v>365420</v>
+        <v>2395259</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>-9502</v>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M38" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Характеристики (объём, размер, гель или без) в ТЗ закрыты (Извещение.zip, часть_II_измененная.docx — zakupki.gov.ru недоступен); среднее НМЦК 13,70 ₽/шт при 15 000 шт «активатор/гель» — если гель, маржа тонкая; ПП 1875: </t>
-        </is>
-      </c>
-      <c r="N38" s="9" t="inlineStr">
+        <v>-250317</v>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: было 33%. Не хватает: ['Подтверждение клиента: правило 3 500 ₽ за китель включает погоны КК, аксельбант, ремень и шеврон или нет (разница 1 848 ₽/шт = 225 тыс. на лот).', 'Подтверждение клиента: шьёт ли он зимнее полупальто (мех. воротник, холлофайбер, съёмный утеплитель) по 5 000</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N38"/>
+  <autoFilter ref="A3:O38"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="По марже" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По марже'!$A$3:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'По марже'!$A$3:$P$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -520,24 +520,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="70" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -560,6 +561,7 @@
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -581,6 +583,7 @@
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -605,55 +608,60 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>Срок договора / поставки</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>Группа</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Предмет</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Заказчик</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>НМЦК, ₽</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Себестоимость + логистика, ₽</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Ожидаемая прибыль, ₽</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Надёжность</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Пересчитано 27.10</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
@@ -678,49 +686,54 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>договор до 01.09.2027 (весь объём в 2026 г.) — план-график</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
           <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>32616496435</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>Поставка спецодежды с защитой от электродуги</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>ООО «Энергонефть Томск» (г. Стрежевой)</t>
         </is>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="J4" s="8" t="n">
         <v>77494934.25</v>
       </c>
-      <c r="J4" s="8" t="n">
+      <c r="K4" s="8" t="n">
         <v>28477107</v>
       </c>
-      <c r="K4" s="8" t="n">
+      <c r="L4" s="8" t="n">
         <v>20739271</v>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="N4" s="9" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>ПЕРЕСЧИТАНО 27.10: было 60%. Не хватает: ['Приложения_к_Извещению.rar (ТЗ) — недоступен (zakupki.gov.ru и etp.gpb.ru из среды не открываются): требуемый ATPV/ЗЭТВ кал/см² и класс защиты по каждой из 12 позиций, ГОСТ (ГОСТ Р 12.4.234/ ГОСТ 12.4.297, ТР ТС 019/2011), цвета, ростовки', 'Вопрос заказчик</t>
         </is>
       </c>
-      <c r="O4" s="10" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -745,45 +758,50 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
+          <t>до 31.12.2026</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
           <t>Пробирки</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>0112200000826004798</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Поставка вакуумных пробирок (дополнительно)для нужд ГБУЗ РТ «Ресбольница №1» 2026 год</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>ГБУЗ Республики Тыва «Республиканская Больница № 1</t>
         </is>
       </c>
-      <c r="I5" s="8" t="n">
+      <c r="J5" s="8" t="n">
         <v>222200</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="K5" s="8" t="n">
         <v>107200</v>
       </c>
-      <c r="K5" s="8" t="n">
+      <c r="L5" s="8" t="n">
         <v>65139</v>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>ТЗ требует завинчивающуюся/поворотную крышку — у МиниМед тип крышки на сайте не указан, подтвердить у производителя до подачи; Требуются насечки на пробирке и крышке — подтвердить; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -808,45 +826,50 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
+          <t>поставка 120 кал. дн. с даты договора</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
           <t>Арматура</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>32616346943</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>Камчатскэнерго: трубопроводная арматура СиНД (315 поз.)</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>АО «Камчатскэнерго» (РусГидро)</t>
         </is>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="J6" s="8" t="n">
         <v>101102908</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="K6" s="8" t="n">
         <v>54810725</v>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="L6" s="8" t="n">
         <v>22809966</v>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>полный построчный расчёт и счета поставщиков (KAMCHATKA_STATUS_2610); 163 позиции ещё не котированы</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>https://zakupki.gov.ru/epz/order/notice/notice223/common-info.html?regNumber=32616346943</t>
         </is>
@@ -857,61 +880,70 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.3891</v>
+        <v>0.372</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Участвовать</t>
+          <t>Участвовать — при опыте 4,85 млн</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>05.11.2026 10:00</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Арматура/ППУ</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>32616491901</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Фасонные изделия и элементы в ППУ изоляции для филиала «Свердловский» ПАО «Т Плюс» (242/27</t>
+          <t>поставка 220 кал. дн. с даты договора</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>11202-РЕМ ПРОД-2027-СЭ</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Т Плюс» (филиал «Свердловский»)</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>8772811.82</v>
+          <t>Сахалинэнерго, лот 2: арматура СиНД для ЮС ТЭЦ-1 (87 поз.)</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
+        </is>
       </c>
       <c r="J7" s="8" t="n">
-        <v>5359602</v>
+        <v>16153216.67</v>
       </c>
       <c r="K7" s="8" t="n">
-        <v>1582213</v>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
+        <v>10149833</v>
+      </c>
+      <c r="L7" s="8" t="n">
+        <v>3063717</v>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M7" s="6" t="inlineStr"/>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>Цены за ед. НМЦК нет (только сумма), маржа оценена по себестоимости 73 позиций (2 058 шт). Источник основных цен — прайс СКТК (с НДС, сметные 2021/22 — на отводах совпадают с ПКФ ТЕПЛО 2026, опоры проиндексированы ×1,25), скользящие опоры — ПКФ ТЕПЛО 2026, концевые — ЛТР. Тип 2 (ППУ2) +10% [оценка].</t>
-        </is>
-      </c>
-      <c r="O7" s="10" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт ≥ 4,85 млн</t>
+        </is>
+      </c>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>https://rushydro.roseltorg.ru</t>
         </is>
       </c>
     </row>
@@ -920,65 +952,66 @@
         <v>5</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.372</v>
+        <v>0.362</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Участвовать — при опыте 4,85 млн</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>05.11.2026 10:00</t>
+          <t>30.10.2026 10:00</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>11202-РЕМ ПРОД-2027-СЭ</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>Сахалинэнерго, лот 2: арматура СиНД для ЮС ТЭЦ-1 (87 поз.)</t>
+          <t>49 кал. дн. с даты контракта</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Одежда/СИЗ/соль</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>0848300064126000376</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
-        </is>
-      </c>
-      <c r="I8" s="8" t="n">
-        <v>16153216.67</v>
+          <t>Поставка модуля пневмокаркасного комбинированного</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>МБУ «Центр по делам ГО и ЧС г.о. Балашиха» (совмес</t>
+        </is>
       </c>
       <c r="J8" s="8" t="n">
-        <v>10149833</v>
+        <v>1355166.67</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>3063717</v>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="inlineStr">
-        <is>
-          <t>ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт ≥ 4,85 млн</t>
-        </is>
-      </c>
-      <c r="O8" s="10" t="inlineStr">
-        <is>
-          <t>https://rushydro.roseltorg.ru</t>
+        <v>865000</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>268986</v>
+      </c>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>Себестоимость — оценка без КП. Запрет иностранного (ПП 1875): модуль и, вероятно, агрегат должны быть российскими с записью в ГИСП. Набор характеристик похож на конкретного производителя модулей для МЧС (Номадика, Арктика, ПневмоСибирь и т.п.) — запросить КП у 2–3 фабрик. Срок изготовления 2–4 недел</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
         </is>
       </c>
     </row>
@@ -987,59 +1020,68 @@
         <v>6</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.362</v>
+        <v>0.352</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 10:00</t>
+          <t>02.11.2026 10:00</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
+          <t>договор до 01.12.2028 (оплата/поставка: 2027, 2028 гг.) — план-график</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
           <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>0848300064126000376</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Поставка модуля пневмокаркасного комбинированного</t>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>32616489407</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>МБУ «Центр по делам ГО и ЧС г.о. Балашиха» (совмес</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>1355166.67</v>
+          <t>МИ №232: спецодежда, спецобувь, СИЗ и дерматологические СИЗ для АО «Уралтурбо»</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>АО «Уралтурбо» (организатор ООО «ГЭХ Закупки»)</t>
+        </is>
       </c>
       <c r="J9" s="8" t="n">
-        <v>865000</v>
+        <v>14973624.91</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>268986</v>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>Себестоимость — оценка без КП. Запрет иностранного (ПП 1875): модуль и, вероятно, агрегат должны быть российскими с записью в ГИСП. Набор характеристик похож на конкретного производителя модулей для МЧС (Номадика, Арктика, ПневмоСибирь и т.п.) — запросить КП у 2–3 фабрик. Срок изготовления 2–4 недел</t>
-        </is>
-      </c>
-      <c r="O9" s="10" t="inlineStr">
+        <v>9703399</v>
+      </c>
+      <c r="L9" s="8" t="n">
+        <v>2844132</v>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: было 38%. Не хватает: ['ТЗ и ценовая форма из 232МИ_кор._от_23.10.zip (zakupki.gov.ru/223/filestore uid=AA9084275251441FB26B2EAABC4DDC40) — нужны марка/класс/объём по каждой позиции; из среды не скачивается (1 попытка, HTTP 000). Запросить у организатора (ssviatova@geh-zakupki.ru)</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1049,64 +1091,65 @@
       <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>0.352</v>
+      <c r="B10" s="12" t="n">
+        <v>0.28</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Участвовать</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 10:00</t>
+          <t>28.10.2026 09:00</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>32616489407</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>МИ №232: спецодежда, спецобувь, СИЗ и дерматологические СИЗ для АО «Уралтурбо»</t>
+          <t>до 17.12.2026</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение/IT</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>0318300028426000179</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>АО «Уралтурбо» (организатор ООО «ГЭХ Закупки»)</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>14973624.91</v>
+          <t>Поставка нейросетевого IP-видеорегистратора TRASSIR для развития АПК «Безопасный город» (Д</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>МКУ МО Динской район «ЕДДС»</t>
+        </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>9703399</v>
+        <v>1525990</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>2844132</v>
-      </c>
-      <c r="L10" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>ПЕРЕСЧИТАНО 27.10: было 38%. Не хватает: ['ТЗ и ценовая форма из 232МИ_кор._от_23.10.zip (zakupki.gov.ru/223/filestore uid=AA9084275251441FB26B2EAABC4DDC40) — нужны марка/класс/объём по каждой позиции; из среды не скачивается (1 попытка, HTTP 000). Запросить у организатора (ssviatova@geh-zakupki.ru)</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="inlineStr">
+        <v>1099000</v>
+      </c>
+      <c r="L10" s="8" t="n">
+        <v>193182</v>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>Подача 28.10 09:00 МСК — 1,5 суток. Бренд задан (TRASSIR, без эквивалента) — цену даёт только DSSL/дистрибьютор по проекту (нужен ИНН заказчика и адрес, у интегратора «Безопасного города» может быть защита проекта → нам дадут цену хуже). Если лицензии на 160 каналов не требуются — себестоимость ~0,5</t>
+        </is>
+      </c>
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1117,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>0.28</v>
+        <v>0.256</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
@@ -1126,50 +1169,55 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 09:00</t>
+          <t>29.10.2026 09:00</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Видеонаблюдение/IT</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>0318300028426000179</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Поставка нейросетевого IP-видеорегистратора TRASSIR для развития АПК «Безопасный город» (Д</t>
+          <t>01.01–31.12.2027, по заявкам до исчерпания суммы</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Пробирки</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>0372100001026000499</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>МКУ МО Динской район «ЕДДС»</t>
-        </is>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>1525990</v>
+          <t>Поставка медицинских изделий (пробирок вакуумных) на 2027 год</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Федеральное ГБУЗ СПБ клиническая больница Российск</t>
+        </is>
       </c>
       <c r="J11" s="8" t="n">
-        <v>1099000</v>
+        <v>1500000</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>193182</v>
-      </c>
-      <c r="L11" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr"/>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>Подача 28.10 09:00 МСК — 1,5 суток. Бренд задан (TRASSIR, без эквивалента) — цену даёт только DSSL/дистрибьютор по проекту (нужен ИНН заказчика и адрес, у интегратора «Безопасного города» может быть защита проекта → нам дадут цену хуже). Если лицензии на 160 каналов не требуются — себестоимость ~0,5</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
+        <v>1116048</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>95251</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>Контракт с неопределённым объёмом (quantityUndefined): цены за ед. (сумма ед. цен 123,84 ₽), поставка по заявкам в 2027 г. до исчерпания 1,5 млн. Доли позиций неизвестны — для расчёта приняты равные доли стоимости.; нет подтверждённого российского аналога (запрет ПП 1875); Упаковка «в штативе из неп</t>
+        </is>
+      </c>
+      <c r="P11" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1180,59 +1228,64 @@
         <v>9</v>
       </c>
       <c r="B12" s="12" t="n">
-        <v>0.256</v>
+        <v>0.234</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>29.10.2026 09:00</t>
+          <t>30.10.2026 07:00</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>0372100001026000499</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>Поставка медицинских изделий (пробирок вакуумных) на 2027 год</t>
+          <t>до 31.12.2026</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение/IT</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>0137100001526000235</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Федеральное ГБУЗ СПБ клиническая больница Российск</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>1500000</v>
+          <t>Поставка терминалов зарядки, архивирования и хранения данных для персональных видеорегистр</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Приокский тыловой таможенный пост (ФТС)</t>
+        </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>1116048</v>
+        <v>4350000</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>95251</v>
-      </c>
-      <c r="L12" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr"/>
-      <c r="N12" s="6" t="inlineStr">
-        <is>
-          <t>Контракт с неопределённым объёмом (quantityUndefined): цены за ед. (сумма ед. цен 123,84 ₽), поставка по заявкам в 2027 г. до исчерпания 1,5 млн. Доли позиций неизвестны — для расчёта приняты равные доли стоимости.; нет подтверждённого российского аналога (запрет ПП 1875); Упаковка «в штативе из неп</t>
-        </is>
-      </c>
-      <c r="O12" s="10" t="inlineStr">
+        <v>3330000</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>377570</v>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>Цена 1,45 млн/шт в 4 раза выше типовых 20-слотовых терминалов → вероятна привязка к конкретной экосистеме (ПО/регистраторы, которые уже есть у таможни), поставку контролирует производитель/дилер. ПП 1875: ограничение (isRestrictForeignPurchaseObjects=true) — нужен товар из реестра российской РЭП (ГИ</t>
+        </is>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1243,59 +1296,68 @@
         <v>10</v>
       </c>
       <c r="B13" s="12" t="n">
-        <v>0.234</v>
+        <v>0.227</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 07:00</t>
+          <t>28.10.2026 10:00</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Видеонаблюдение/IT</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>0137100001526000235</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>Поставка терминалов зарядки, архивирования и хранения данных для персональных видеорегистр</t>
+          <t>договор до 01.12.2029 (оплата/поставка: 2027, 2028, 2029 гг.) — план-график</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Одежда/СИЗ/соль</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>32616489910</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Приокский тыловой таможенный пост (ФТС)</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>4350000</v>
+          <t>МИ №308: поставка соли технической для Химкинского филиала ООО «ТСК Мосэнерго»</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Теплоснабжающая компания Мосэнерго» (организа</t>
+        </is>
       </c>
       <c r="J13" s="8" t="n">
-        <v>3330000</v>
+        <v>44596673</v>
       </c>
       <c r="K13" s="8" t="n">
-        <v>377570</v>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr"/>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>Цена 1,45 млн/шт в 4 раза выше типовых 20-слотовых терминалов → вероятна привязка к конкретной экосистеме (ПО/регистраторы, которые уже есть у таможни), поставку контролирует производитель/дилер. ПП 1875: ограничение (isRestrictForeignPurchaseObjects=true) — нужен товар из реестра российской РЭП (ГИ</t>
-        </is>
-      </c>
-      <c r="O13" s="10" t="inlineStr">
+        <v>34471162</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>3579732</v>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ПЕРЕСЧИТАНО 27.10: было 36%. Не хватает: ['308_МИ.rar (ТЗ) — недоступен (zakupki.gov.ru/etp.gpb.ru не отвечают): тоннаж навала и таблеток по годам, ГОСТ/тип (ГОСТ Р 51574 / ГОСТ 13830, тип/сорт, NaCl ≥97–99%, антислеживатель), точки поставки (одна котельная/ТЭЦ или несколько), способ (ж/д или авто, </t>
+        </is>
+      </c>
+      <c r="P13" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1306,7 +1368,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="12" t="n">
-        <v>0.227</v>
+        <v>0.21</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -1315,54 +1377,55 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 10:00</t>
+          <t>29.10.2026 09:30</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
+          <t>до 30.11.2026</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
           <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>32616489910</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>МИ №308: поставка соли технической для Химкинского филиала ООО «ТСК Мосэнерго»</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>0327300018526000001</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>ООО «Теплоснабжающая компания Мосэнерго» (организа</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>44596673</v>
+          <t>Поставка хоккейной экипировки</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>МБУ «ФОК» г. Новозыбкова (описание объекта — МБУДО</t>
+        </is>
       </c>
       <c r="J14" s="8" t="n">
-        <v>34471162</v>
+        <v>2999795.9</v>
       </c>
       <c r="K14" s="8" t="n">
-        <v>3579732</v>
-      </c>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ПЕРЕСЧИТАНО 27.10: было 36%. Не хватает: ['308_МИ.rar (ТЗ) — недоступен (zakupki.gov.ru/etp.gpb.ru не отвечают): тоннаж навала и таблеток по годам, ГОСТ/тип (ГОСТ Р 51574 / ГОСТ 13830, тип/сорт, NaCl ≥97–99%, антислеживатель), точки поставки (одна котельная/ТЭЦ или несколько), способ (ж/д или авто, </t>
-        </is>
-      </c>
-      <c r="O14" s="10" t="inlineStr">
+        <v>2369841</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>195895</v>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>50 позиций, в основном импортные бренды. В закупке действует ограничение для иностранных товаров (isRestrictForeignPurchaseObjects): при одной заявке с российским товаром импортные отклоняются, а российских производителей экипировки мало. Маржа тонкая (≈20% до торга): НМЦК собран по рознице. Нужен п</t>
+        </is>
+      </c>
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1373,196 +1436,199 @@
         <v>12</v>
       </c>
       <c r="B15" s="12" t="n">
-        <v>0.2143</v>
+        <v>0.2</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 12:00</t>
+          <t>28.10.2026 11:00</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Арматура/ППУ</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>32616495280</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>Фасонные изделия и элементы в ППУ изоляции для нужд АО «ЕТК» (244/27, 4651032)</t>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Одежда/СИЗ/соль</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>B2010261157408</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>АО «Екатеринбургская Теплосетевая Компания»</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>46388455.4</v>
+          <t>Поставка армейских палаток для филиалов АНО ДПО «ВОИН» (Амурская обл., ЕАО, Карелия, Примо</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>АНО ДПО «Центр развития военно-спортивной подготов</t>
+        </is>
       </c>
       <c r="J15" s="8" t="n">
-        <v>36449290</v>
+        <v>2210933.36</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>1247054</v>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
+        <v>1768747</v>
+      </c>
+      <c r="L15" s="8" t="n">
+        <v>124970</v>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M15" s="6" t="inlineStr"/>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>Цены за ед. НМЦК нет. 60% себестоимости — Ду 720–1020 (отводы 820х11 ×26, опоры 720 ×34, опоры 820/1020 со щитами): цены на них в открытых прайсах только у Сайверхот (розница: 720х8 165 тыс., 820х9 346 тыс.) — пересчитаны ×1,1 стенка ×0,85 [оценка]; неподвижные опоры 720–1020 — экстраполяция [оценка</t>
-        </is>
-      </c>
-      <c r="O15" s="10" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
+      <c r="N15" s="6" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>Спецификация недоступна, модель и количество неизвестны. Доставка в 4 удалённых точки (Петрозаводск, Благовещенск, Владивосток, Хабаровск) — дорогая логистика, около 5% [оценка]. До подачи меньше 2 суток (28.10 11:00). Подавать, только если сегодня-завтра получим ТЗ и КП фабрики (ПК «Агролиз», Пневм</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>0.21</v>
+      <c r="B16" s="13" t="n">
+        <v>0.1966</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>29.10.2026 09:30</t>
+          <t>30.10.2026 10:00</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>0327300018526000001</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Поставка хоккейной экипировки</t>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>8083</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>МБУ «ФОК» г. Новозыбкова (описание объекта — МБУДО</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>2999795.9</v>
+          <t>Поставка арматуры трубопроводной</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Ремонтно-механический завод» (Салават)</t>
+        </is>
       </c>
       <c r="J16" s="8" t="n">
-        <v>2369841</v>
+        <v>18813618</v>
       </c>
       <c r="K16" s="8" t="n">
-        <v>195895</v>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
+        <v>15114861</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>1007259</v>
+      </c>
+      <c r="M16" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr"/>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>50 позиций, в основном импортные бренды. В закупке действует ограничение для иностранных товаров (isRestrictForeignPurchaseObjects): при одной заявке с российским товаром импортные отклоняются, а российских производителей экипировки мало. Маржа тонкая (≈20% до торга): НМЦК собран по рознице. Нужен п</t>
-        </is>
-      </c>
-      <c r="O16" s="10" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
+      <c r="N16" s="6" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="n">
-        <v>0.2081</v>
+      <c r="B17" s="13" t="n">
+        <v>0.1966</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>05.11.2026 12:00</t>
+          <t>28.10.2026 13:00</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Арматура/ППУ</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>32616501405</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>Поставка труб ПЭ100 и ПП, фитингов в ассортименте</t>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>8004</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>ООО «СМЭУ «Заневка»</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="n">
-        <v>7019054.69</v>
+          <t>Затвор дисковый (56-100)</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Ремонтно-механический завод» (Салават)</t>
+        </is>
       </c>
       <c r="J17" s="8" t="n">
-        <v>5558195</v>
+        <v>10474222</v>
       </c>
       <c r="K17" s="8" t="n">
-        <v>446830</v>
-      </c>
-      <c r="L17" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>87% суммы — труба 225 мм (2 990 м по 2 044 ₽). SDR в ЕИС не указан (ТЗ в Прил.1 — zakupki.gov.ru недоступен): при SDR17 маржа ок, при SDR11 (2 278 ₽/м) себестоимость 7.63 млн ≈ НМЦК → убыток. Втулка 225 по рынку 1 331 &gt; НМЦК 990. Нацрежим: ограничение (ПП 1875) по ПЭ-позициям — нужен российский прои</t>
-        </is>
-      </c>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
+        <v>8414990</v>
+      </c>
+      <c r="L17" s="8" t="n">
+        <v>560778</v>
+      </c>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="12" t="n">
-        <v>0.2</v>
+      <c r="B18" s="13" t="n">
+        <v>0.1966</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -1571,50 +1637,55 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 11:00</t>
+          <t>02.11.2026 13:00</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>B2010261157408</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>Поставка армейских палаток для филиалов АНО ДПО «ВОИН» (Амурская обл., ЕАО, Карелия, Примо</t>
+          <t>до 09.12.2026 (поставка 10 раб. дн.)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>7600</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>АНО ДПО «Центр развития военно-спортивной подготов</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>2210933.36</v>
+          <t>Поставка затворов</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Ремонтно-механический завод» (Салават)</t>
+        </is>
       </c>
       <c r="J18" s="8" t="n">
-        <v>1768747</v>
+        <v>5271798.95</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>124970</v>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
+        <v>4235363</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>282246</v>
+      </c>
+      <c r="M18" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr"/>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>Спецификация недоступна, модель и количество неизвестны. Доставка в 4 удалённых точки (Петрозаводск, Благовещенск, Владивосток, Хабаровск) — дорогая логистика, около 5% [оценка]. До подачи меньше 2 суток (28.10 11:00). Подавать, только если сегодня-завтра получим ТЗ и КП фабрики (ПК «Агролиз», Пневм</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -1630,50 +1701,55 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 10:00</t>
+          <t>28.10.2026 13:00</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
+          <t>до 31.12.2026</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
           <t>Арматура</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>8083</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>Поставка арматуры трубопроводной</t>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>8002</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
+          <t>Запорная арматура</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
           <t>ООО «Ремонтно-механический завод» (Салават)</t>
         </is>
       </c>
-      <c r="I19" s="8" t="n">
-        <v>18813618</v>
-      </c>
       <c r="J19" s="8" t="n">
-        <v>15114861</v>
+        <v>4248523</v>
       </c>
       <c r="K19" s="8" t="n">
-        <v>1007259</v>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
+        <v>3413263</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>227461</v>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr"/>
-      <c r="N19" s="6" t="inlineStr">
+      <c r="N19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
         </is>
       </c>
-      <c r="O19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -1689,286 +1765,319 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 13:00</t>
+          <t>28.10.2026 12:00</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
           <t>Арматура</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>8004</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Затвор дисковый (56-100)</t>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>ГП646025</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>ООО «Ремонтно-механический завод» (Салават)</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>10474222</v>
+          <t>Закупка ЗРА и КОФ (890)</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>ООО «НПП «Нефтехимия» (Москва, ИНН 7723332561)</t>
+        </is>
       </c>
       <c r="J20" s="8" t="n">
-        <v>8414990</v>
+        <v>2000000</v>
       </c>
       <c r="K20" s="8" t="n">
-        <v>560778</v>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
+        <v>1606800</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>107078</v>
+      </c>
+      <c r="M20" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M20" s="6" t="inlineStr"/>
-      <c r="N20" s="6" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
-        </is>
-      </c>
-      <c r="O20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>НПП «Нефтехимия» — производство полипропилена на площадке МНПЗ (Капотня), нефтехим: вероятны 09Г2С/нерж., класс А, ТР ТС 032 (опасные среды), возможна проверка поставщика службой безопасности. Срок 28.10 12:00 — 2 дня, нужен быстрый КП завода. Состав позиций неизвестен.</t>
+        </is>
+      </c>
+      <c r="P20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="4" t="n">
         <v>18</v>
       </c>
       <c r="B21" s="13" t="n">
-        <v>0.1966</v>
+        <v>0.1965</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Участвовать</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 13:00</t>
+          <t>28.10.2026 10:00</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
+          <t>договор до 01.12.2026 — план-график</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
           <t>Арматура</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>7600</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Поставка затворов</t>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>32616480814</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>ООО «Ремонтно-механический завод» (Салават)</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>5271798.95</v>
+          <t>Поставка запорной арматуры (задвижки 30с41нж/30с941нж Ду50–200, 70 шт)</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>АО «Петербургский Нефтяной Терминал» (ИНН 78050580</t>
+        </is>
       </c>
       <c r="J21" s="8" t="n">
-        <v>4235363</v>
+        <v>3163250.24</v>
       </c>
       <c r="K21" s="8" t="n">
-        <v>282246</v>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="inlineStr"/>
-      <c r="N21" s="6" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
-        </is>
-      </c>
-      <c r="O21" s="6" t="inlineStr"/>
+        <v>2541597</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>169144</v>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>Позиции из ЕИС (8 строк, 70 шт). Ред.3 от 22.10: изменена марка стали в ТЗ (новая ТЗ не скачана — zakupki.gov.ru недоступен) → расчёт консервативно на 09Г2С (30лс41нж), себестоимость ≈2.50 млн. Если сталь 20Л/25Л (обычные 30с41нж) — себестоимость ≈1.28 млн, маржа ~55%. Если 30с941нж — с электроприво</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="4" t="n">
         <v>19</v>
       </c>
       <c r="B22" s="13" t="n">
-        <v>0.1966</v>
+        <v>0.1888</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 13:00</t>
+          <t>03.11.2026 08:00</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
           <t>Арматура</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>8002</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Запорная арматура</t>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>1029143</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>ООО «Ремонтно-механический завод» (Салават)</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>4248523</v>
+          <t>Затворы дисковые поворотные 2027</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Филиал «Пензенский» ПАО «Т Плюс» (Пенза, Ново-Черк</t>
+        </is>
       </c>
       <c r="J22" s="8" t="n">
-        <v>3413263</v>
+        <v>303969.42</v>
       </c>
       <c r="K22" s="8" t="n">
-        <v>227461</v>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
+        <v>246580</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>14193</v>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M22" s="6" t="inlineStr"/>
-      <c r="N22" s="6" t="inlineStr">
-        <is>
-          <t>ООО «РМЗ» (Салават, ИНН 0266033773, контур «Газпром нефтехим Салават»). Карточки torgi-rf.ru закрыты логином (303→/login, API 401), в агрегаторах нет — состав позиций неизвестен. Серия лотов одного заказчика: 7600 (опубл. 29.09, срок продлён с 21.10 до 02.11), 8002/8004 (опубл. 19.10, продлены с 26.</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>Малый лот (0,3 млн), поставка в 2027. Т Плюс — запрос цен на ЭТП ГПБ, обычно требует регистрации в реестре поставщиков Т Плюс и цены «без НДС/с НДС» — у нас без НДС (сравнение может быть без НДС → потеря ~18% конкурентности). Доставка Пенза — небольшая. Чистая прибыль ~25 тыс. — участвовать только е</t>
+        </is>
+      </c>
+      <c r="P22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="B23" s="13" t="n">
-        <v>0.1966</v>
+        <v>0.188</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 12:00</t>
+          <t>30.10.2026 07:00</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>ГП646025</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>Закупка ЗРА и КОФ (890)</t>
+          <t>до 22.12.2026</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Пробирки</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>0860200000826008623</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>ООО «НПП «Нефтехимия» (Москва, ИНН 7723332561)</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>2000000</v>
+          <t>Поставка пробирок</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>ГУЧ Здравоохранения «Саратовская Городская Поликли</t>
+        </is>
       </c>
       <c r="J23" s="8" t="n">
-        <v>1606800</v>
+        <v>126000</v>
       </c>
       <c r="K23" s="8" t="n">
-        <v>107078</v>
-      </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M23" s="6" t="inlineStr"/>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>НПП «Нефтехимия» — производство полипропилена на площадке МНПЗ (Капотня), нефтехим: вероятны 09Г2С/нерж., класс А, ТР ТС 032 (опасные среды), возможна проверка поставщика службой безопасности. Срок 28.10 12:00 — 2 дня, нужен быстрый КП завода. Состав позиций неизвестен.</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr"/>
+        <v>102340</v>
+      </c>
+      <c r="L23" s="8" t="n">
+        <v>5770</v>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="4" t="n">
         <v>21</v>
       </c>
       <c r="B24" s="13" t="n">
-        <v>0.1965</v>
+        <v>0.179</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Участвовать</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 10:00</t>
+          <t>03.11.2026 09:00</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>32616480814</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>Поставка запорной арматуры (задвижки 30с41нж/30с941нж Ду50–200, 70 шт)</t>
+          <t>договор до 01.12.2026 — план-график</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Одежда/СИЗ/соль</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>32616497619</t>
         </is>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>АО «Петербургский Нефтяной Терминал» (ИНН 78050580</t>
-        </is>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>3163250.24</v>
+          <t>Поставка спецодежды, спецобуви и средств индивидуальной и коллективной защиты</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>МУП «Водоканал» г. Белорецк</t>
+        </is>
       </c>
       <c r="J24" s="8" t="n">
-        <v>2541597</v>
+        <v>1264480.67</v>
       </c>
       <c r="K24" s="8" t="n">
-        <v>169144</v>
-      </c>
-      <c r="L24" s="6" t="inlineStr">
+        <v>1038520</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>26501</v>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr"/>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>Позиции из ЕИС (8 строк, 70 шт). Ред.3 от 22.10: изменена марка стали в ТЗ (новая ТЗ не скачана — zakupki.gov.ru недоступен) → расчёт консервативно на 09Г2С (30лс41нж), себестоимость ≈2.50 млн. Если сталь 20Л/25Л (обычные 30с41нж) — себестоимость ≈1.28 млн, маржа ~55%. Если 30с941нж — с электроприво</t>
-        </is>
-      </c>
-      <c r="O24" s="10" t="inlineStr">
+      <c r="N24" s="6" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Тонко: безубыточное снижение ~14,5%, при снижении 12% net ~26 тыс. Подавать с ценой не ниже −5…−8% от НМЦК. Конкурс: кроме цены оцениваются критерии (опыт, квалификация — «Таблица оценочных критериев.xlsx»), без опыта шансы ниже. 82% себестоимости — зимние костюмы по правилу клиента 5 000 ₽; если в </t>
+        </is>
+      </c>
+      <c r="P24" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -1979,118 +2088,128 @@
         <v>22</v>
       </c>
       <c r="B25" s="13" t="n">
-        <v>0.1888</v>
+        <v>0.177</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>03.11.2026 08:00</t>
+          <t>30.10.2026 15:00</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>1029143</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>Затворы дисковые поворотные 2027</t>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение/IT</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>SBR063-260750911700213</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Филиал «Пензенский» ПАО «Т Плюс» (Пенза, Ново-Черк</t>
-        </is>
-      </c>
-      <c r="I25" s="8" t="n">
-        <v>303969.42</v>
+          <t>7714-OD Приобретение видеорегистраторов для системы видеонаблюдения КТК-Р</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>АО «Каспийский Трубопроводный Консорциум-Р»</t>
+        </is>
       </c>
       <c r="J25" s="8" t="n">
-        <v>246580</v>
+        <v>30287213.11</v>
       </c>
       <c r="K25" s="8" t="n">
-        <v>14193</v>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
+        <v>24925515</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>1101124</v>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="M25" s="6" t="inlineStr"/>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>Малый лот (0,3 млн), поставка в 2027. Т Плюс — запрос цен на ЭТП ГПБ, обычно требует регистрации в реестре поставщиков Т Плюс и цены «без НДС/с НДС» — у нас без НДС (сравнение может быть без НДС → потеря ~18% конкурентности). Доставка Пенза — небольшая. Чистая прибыль ~25 тыс. — участвовать только е</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr"/>
+      <c r="N25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>Позиции/бренды неизвестны (КТК часто задаёт конкретные бренды и номенклатуру по проекту, двуязычная документация, квалификация/проверка контрагента КТК, опыт аналогичных поставок). 30 млн — большой оборотный капитал на 60+ дней; вероятно оплата по факту поставки. ПП 1875 к КТК-Р формально не применя</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="4" t="n">
         <v>23</v>
       </c>
       <c r="B26" s="13" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 07:00</t>
+          <t>02.11.2026 10:30</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr">
-        <is>
-          <t>0860200000826008623</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Поставка пробирок</t>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Видеонаблюдение/IT</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>32616501691</t>
         </is>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>ГУЧ Здравоохранения «Саратовская Городская Поликли</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="n">
-        <v>126000</v>
+          <t>Поставка оборудования и комплектующих для системы мониторинга ЕИСБ для нужд филиала ПАО «Р</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>ПАО «Россети Центр и Приволжье»</t>
+        </is>
       </c>
       <c r="J26" s="8" t="n">
-        <v>102340</v>
+        <v>3588800.8</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>5770</v>
-      </c>
-      <c r="L26" s="6" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M26" s="6" t="inlineStr"/>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
-        </is>
-      </c>
-      <c r="O26" s="10" t="inlineStr">
+        <v>2957500</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>126946</v>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N26" s="6" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>Спецификация в RAR на ЕИС (недоступен) — модели/характеристики неизвестны, nmck_unit распределены пропорционально оценочным ценам. ПП 1875 ограничение по 10 из 15 позиций (регистраторы, HDD, мониторы, камеры, ВКС, телеком) — нужны товары из реестра РЭП; HDD российского производства в реестре практич</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2101,7 +2220,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="13" t="n">
-        <v>0.179</v>
+        <v>0.175</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
@@ -2110,172 +2229,191 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>03.11.2026 09:00</t>
+          <t>30.10.2026 12:00</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
+          <t>поставка 10 кал. дн. с даты договора, оплата 30 дн. после приёмки</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
           <t>Одежда/СИЗ/соль</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>32616497619</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Поставка спецодежды, спецобуви и средств индивидуальной и коллективной защиты</t>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>B1510261835045</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>МУП «Водоканал» г. Белорецк</t>
-        </is>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>1264480.67</v>
+          <t>Таврида.Арт: форменная одежда службы безопасности</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>АНО «Таврида.Арт»</t>
+        </is>
       </c>
       <c r="J27" s="8" t="n">
-        <v>1038520</v>
+        <v>4169750</v>
       </c>
       <c r="K27" s="8" t="n">
-        <v>26501</v>
-      </c>
-      <c r="L27" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M27" s="6" t="inlineStr"/>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Тонко: безубыточное снижение ~14,5%, при снижении 12% net ~26 тыс. Подавать с ценой не ниже −5…−8% от НМЦК. Конкурс: кроме цены оцениваются критерии (опыт, квалификация — «Таблица оценочных критериев.xlsx»), без опыта шансы ниже. 82% себестоимости — зимние костюмы по правилу клиента 5 000 ₽; если в </t>
-        </is>
-      </c>
-      <c r="O27" s="10" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
+        <v>3440900</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>319215</v>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>построчно сверено (TAVRIDA_FINAL_2010); идти при подтверждённом наличии</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="4" t="n">
         <v>25</v>
       </c>
       <c r="B28" s="13" t="n">
-        <v>0.177</v>
+        <v>0.1696</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 15:00</t>
+          <t>30.10.2026 12:00</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Видеонаблюдение/IT</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>SBR063-260750911700213</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>7714-OD Приобретение видеорегистраторов для системы видеонаблюдения КТК-Р</t>
+          <t>в документации (ЕИС/площадка недоступны)</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Арматура/ППУ</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>32616491901</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>АО «Каспийский Трубопроводный Консорциум-Р»</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="n">
-        <v>30287213.11</v>
+          <t>Фасонные изделия и элементы в ППУ изоляции для филиала «Свердловский» ПАО «Т Плюс» (242/27</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>ПАО «Т Плюс» (филиал «Свердловский»)</t>
+        </is>
       </c>
       <c r="J28" s="8" t="n">
-        <v>24925515</v>
+        <v>8772811.82</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>1101124</v>
-      </c>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M28" s="6" t="inlineStr"/>
-      <c r="N28" s="6" t="inlineStr">
-        <is>
-          <t>Позиции/бренды неизвестны (КТК часто задаёт конкретные бренды и номенклатуру по проекту, двуязычная документация, квалификация/проверка контрагента КТК, опыт аналогичных поставок). 30 млн — большой оборотный капитал на 60+ дней; вероятно оплата по факту поставки. ПП 1875 к КТК-Р формально не применя</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr"/>
+        <v>7284540</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>-126797</v>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: было 39%. Не хватает: ['242-27 Документация.zip (ЕИС) недоступна (zakupki.gov.ru не открывается из среды): нет обоснования НМЦ по позициям — nmck_unit распределены пропорционально себестоимости; нет ТЗ (длина плеч отводов, тип ОДК, требования к ЗМКТ/К/В, марка стали для позиций бе</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="4" t="n">
         <v>26</v>
       </c>
       <c r="B29" s="13" t="n">
-        <v>0.176</v>
+        <v>0.161</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>02.11.2026 10:30</t>
+          <t>03.11.2026 07:00</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
+          <t>до 31.12.2026</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
           <t>Видеонаблюдение/IT</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>32616501691</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Поставка оборудования и комплектующих для системы мониторинга ЕИСБ для нужд филиала ПАО «Р</t>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>0829500001126007015</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Россети Центр и Приволжье»</t>
-        </is>
-      </c>
-      <c r="I29" s="8" t="n">
-        <v>3588800.8</v>
+          <t>Поставка оборудования для организации видеонаблюдения</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>ГБУЗ «Клиническая станция скорой медицинской помощ</t>
+        </is>
       </c>
       <c r="J29" s="8" t="n">
-        <v>2957500</v>
+        <v>2081541.45</v>
       </c>
       <c r="K29" s="8" t="n">
-        <v>126946</v>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M29" s="6" t="inlineStr"/>
-      <c r="N29" s="6" t="inlineStr">
-        <is>
-          <t>Спецификация в RAR на ЕИС (недоступен) — модели/характеристики неизвестны, nmck_unit распределены пропорционально оценочным ценам. ПП 1875 ограничение по 10 из 15 позиций (регистраторы, HDD, мониторы, камеры, ВКС, телеком) — нужны товары из реестра РЭП; HDD российского производства в реестре практич</t>
-        </is>
-      </c>
-      <c r="O29" s="10" t="inlineStr">
+        <v>1747300</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>45607</v>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>Маржа тонкая (~12%). ПП 1875 ОГРАНИЧЕНИЕ по камерам, коммутаторам, кабелю, NVR и HDD: если хотя бы один участник даст реестровый товар — наша заявка с иностранным (HiWatch/Dahua) будет отклонена; реестровые камеры/коммутаторы (TRASSIR) дороже НМЦК. Кабель — есть российские производители (выгодно бра</t>
+        </is>
+      </c>
+      <c r="P29" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2286,118 +2424,136 @@
         <v>27</v>
       </c>
       <c r="B30" s="13" t="n">
-        <v>0.175</v>
+        <v>0.144</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Осторожно — только после КП АРМАТЭК</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>30.10.2026 12:00</t>
+          <t>05.11.2026 10:00</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Одежда/СИЗ/соль</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>B1510261835045</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Таврида.Арт: форменная одежда службы безопасности</t>
+          <t>поставка 230 кал. дн. с даты договора</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Арматура</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>11201-РЕМ ПРОД-2027-СЭ</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>АНО «Таврида.Арт»</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>4169750</v>
+          <t>Сахалинэнерго, лот 1: арматура СиНД для Сахалинской ГРЭС (83 поз.)</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
+        </is>
       </c>
       <c r="J30" s="8" t="n">
-        <v>3440900</v>
+        <v>12269140</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>319215</v>
-      </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr"/>
-      <c r="N30" s="6" t="inlineStr">
-        <is>
-          <t>построчно сверено (TAVRIDA_FINAL_2010); идти при подтверждённом наличии</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr"/>
+        <v>10507218</v>
+      </c>
+      <c r="L30" s="8" t="n">
+        <v>-354638</v>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: все 83 позиции + доставка; 39% НМЦ — оценка (затворы АРМАТЭК АМ 2,4 млн — цены нет); 16 убыточных строк; при снижении &gt;7% — минус</t>
+        </is>
+      </c>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>https://rushydro.roseltorg.ru</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="4" t="n">
         <v>28</v>
       </c>
       <c r="B31" s="13" t="n">
-        <v>0.161</v>
+        <v>0.124</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Осторожно</t>
+          <t>Запросить спецификацию</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>03.11.2026 07:00</t>
+          <t>09.11.2026 09:00</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
+          <t>договор до 01.01.2027 (весь объём в 2027 г.) — план-график</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
           <t>Видеонаблюдение/IT</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>0829500001126007015</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Поставка оборудования для организации видеонаблюдения</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>32616494964</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>ГБУЗ «Клиническая станция скорой медицинской помощ</t>
-        </is>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>2081541.45</v>
+          <t>Поставка вычислительной техники, оргтехники и офисного оборудования</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>АО «Охинская ТЭЦ»</t>
+        </is>
       </c>
       <c r="J31" s="8" t="n">
-        <v>1747300</v>
+        <v>2900149.68</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>45607</v>
-      </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr"/>
-      <c r="N31" s="6" t="inlineStr">
-        <is>
-          <t>Маржа тонкая (~12%). ПП 1875 ОГРАНИЧЕНИЕ по камерам, коммутаторам, кабелю, NVR и HDD: если хотя бы один участник даст реестровый товар — наша заявка с иностранным (HiWatch/Dahua) будет отклонена; реестровые камеры/коммутаторы (TRASSIR) дороже НМЦК. Кабель — есть российские производители (выгодно бра</t>
-        </is>
-      </c>
-      <c r="O31" s="10" t="inlineStr">
+        <v>2540000</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>-34253</v>
+      </c>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>ТЗ и форма КП есть на ЕИС (docx/xlsx), но не скачаны — модели/конфигурации ПК неизвестны; оценка состава 2,45 млн против НМЦК 2,9 млн. Доставка в Оху (север Сахалина) — дорогая и долгая логистика (~3% НМЦК). ПП 1875 ограничение по 7 из 8 позиций — ПК, мониторы, принтеры, регистраторы нужны из реестр</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2407,66 +2563,67 @@
       <c r="A32" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="13" t="n">
-        <v>0.144</v>
+      <c r="B32" s="14" t="n">
+        <v>0.09699999999999999</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Осторожно — только после КП АРМАТЭК</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>05.11.2026 10:00</t>
+          <t>28.10.2026 05:00</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Арматура</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>11201-РЕМ ПРОД-2027-СЭ</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>Сахалинэнерго, лот 1: арматура СиНД для Сахалинской ГРЭС (83 поз.)</t>
+          <t>до 31.12.2026</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>Пробирки</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>0334200012526000832</t>
         </is>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>ПАО «Сахалинэнерго» (РусГидро)</t>
-        </is>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>12269140</v>
+          <t>Поставка пробирок</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>ГБУЗ Иркутская ордена «Знак Почета» областная клин</t>
+        </is>
       </c>
       <c r="J32" s="8" t="n">
-        <v>10507218</v>
+        <v>253140</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>-354638</v>
-      </c>
-      <c r="L32" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M32" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="inlineStr">
-        <is>
-          <t>ПЕРЕСЧИТАНО 27.10: все 83 позиции + доставка; 39% НМЦ — оценка (затворы АРМАТЭК АМ 2,4 млн — цены нет); 16 убыточных строк; при снижении &gt;7% — минус</t>
-        </is>
-      </c>
-      <c r="O32" s="10" t="inlineStr">
-        <is>
-          <t>https://rushydro.roseltorg.ru</t>
+        <v>228620</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>2059</v>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr"/>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="inlineStr">
+        <is>
+          <t>ЕИС</t>
         </is>
       </c>
     </row>
@@ -2474,60 +2631,65 @@
       <c r="A33" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B33" s="13" t="n">
-        <v>0.124</v>
+      <c r="B33" s="14" t="n">
+        <v>0.08800000000000001</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Запросить спецификацию</t>
+          <t>Осторожно</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>09.11.2026 09:00</t>
+          <t>01.11.2026 17:00</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Видеонаблюдение/IT</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>32616494964</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Поставка вычислительной техники, оргтехники и офисного оборудования</t>
+          <t>до 10.08.2027 (поставки этапами до 10.12.2026 и 15.02.2027)</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Пробирки</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>0322200005226000562</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>АО «Охинская ТЭЦ»</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>2900149.68</v>
+          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД, с активатором свертывания</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Краевое ГБУЗ «Краевая Клиническая Психиатрическая </t>
+        </is>
       </c>
       <c r="J33" s="8" t="n">
-        <v>2540000</v>
+        <v>422090</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>-34253</v>
-      </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M33" s="6" t="inlineStr"/>
-      <c r="N33" s="6" t="inlineStr">
-        <is>
-          <t>ТЗ и форма КП есть на ЕИС (docx/xlsx), но не скачаны — модели/конфигурации ПК неизвестны; оценка состава 2,45 млн против НМЦК 2,9 млн. Доставка в Оху (север Сахалина) — дорогая и долгая логистика (~3% НМЦК). ПП 1875 ограничение по 7 из 8 позиций — ПК, мониторы, принтеры, регистраторы нужны из реестр</t>
-        </is>
-      </c>
-      <c r="O33" s="10" t="inlineStr">
+        <v>385000</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>13 мм на 9–9,5 мл не выпускается (МиниМед 13×100 макс. 7 мл; 9 мл — только 16×100) — характеристика неисполнима, нужен запрос разъяснений; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2538,7 +2700,7 @@
         <v>31</v>
       </c>
       <c r="B34" s="14" t="n">
-        <v>0.09699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -2547,50 +2709,55 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>28.10.2026 05:00</t>
+          <t>01.11.2026 17:00</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
+          <t>до 10.08.2027 (поставки этапами до 10.12.2026 и 15.02.2027)</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
           <t>Пробирки</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>0334200012526000832</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>Поставка пробирок</t>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>0322200005226000561</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>ГБУЗ Иркутская ордена «Знак Почета» областная клин</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>253140</v>
+          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Краевое ГБУЗ «Краевая Клиническая Психиатрическая </t>
+        </is>
       </c>
       <c r="J34" s="8" t="n">
-        <v>228620</v>
+        <v>484797</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>2059</v>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="M34" s="6" t="inlineStr"/>
-      <c r="N34" s="6" t="inlineStr">
-        <is>
-          <t>ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
-        </is>
-      </c>
-      <c r="O34" s="10" t="inlineStr">
+        <v>442680</v>
+      </c>
+      <c r="L34" s="8" t="n">
+        <v>-361</v>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr"/>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>Убыточные строки (себес &gt; НМЦК ед.): с натрия цитратом [Концентрация цитрата натрия=3.8, D=13, H=; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2601,7 +2768,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="14" t="n">
-        <v>0.08800000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
@@ -2610,50 +2777,55 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>01.11.2026 17:00</t>
+          <t>29.10.2026 07:00</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
+          <t>договор до 01.06.2027 (оплата/поставка: 2026, 2027 гг.) — план-график</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
           <t>Пробирки</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>0322200005226000562</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД, с активатором свертывания</t>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>32616494976</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Краевое ГБУЗ «Краевая Клиническая Психиатрическая </t>
-        </is>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>422090</v>
+          <t>Поставка изделий медицинского назначения (пробирки вакуумные)</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Государственное автономное учреждение Здравоохране</t>
+        </is>
       </c>
       <c r="J35" s="8" t="n">
-        <v>385000</v>
+        <v>390420</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>102</v>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr"/>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>13 мм на 9–9,5 мл не выпускается (МиниМед 13×100 макс. 7 мл; 9 мл — только 16×100) — характеристика неисполнима, нужен запрос разъяснений; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
-        </is>
-      </c>
-      <c r="O35" s="10" t="inlineStr">
+        <v>365420</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>-9502</v>
+      </c>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>Характеристики (объём, размер, гель или без) в ТЗ закрыты (Извещение.zip, часть_II_измененная.docx — zakupki.gov.ru недоступен); среднее НМЦК 13,70 ₽/шт при 15 000 шт «активатор/гель» — если гель, маржа тонкая; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/Г</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
@@ -2664,7 +2836,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="14" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.038</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
@@ -2673,214 +2845,91 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>01.11.2026 17:00</t>
+          <t>02.11.2026 10:00</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>0322200005226000561</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>Поставка пробирок вакуумных для взятия образцов крови ИВД</t>
+          <t>до 31.12.2026</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>Одежда/СИЗ/соль</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>0372200087626000024</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Краевое ГБУЗ «Краевая Клиническая Психиатрическая </t>
-        </is>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>484797</v>
+          <t>Поставка кадетской формы в 2026 году</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>ГБОУ Школа № 380 Красносельского р-на СПб им. А.И.</t>
+        </is>
       </c>
       <c r="J36" s="8" t="n">
-        <v>442680</v>
+        <v>2490692</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>-361</v>
-      </c>
-      <c r="L36" s="6" t="inlineStr">
+        <v>2395259</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>-250317</v>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="M36" s="6" t="inlineStr"/>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>Убыточные строки (себес &gt; НМЦК ед.): с натрия цитратом [Концентрация цитрата натрия=3.8, D=13, H=; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/ГИСП), маркировка «Честный знак»</t>
-        </is>
-      </c>
-      <c r="O36" s="10" t="inlineStr">
+      <c r="N36" s="9" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>ПЕРЕСЧИТАНО 27.10: было 33%. Не хватает: ['Подтверждение клиента: правило 3 500 ₽ за китель включает погоны КК, аксельбант, ремень и шеврон или нет (разница 1 848 ₽/шт = 225 тыс. на лот).', 'Подтверждение клиента: шьёт ли он зимнее полупальто (мех. воротник, холлофайбер, съёмный утеплитель) по 5 000</t>
+        </is>
+      </c>
+      <c r="P36" s="10" t="inlineStr">
         <is>
           <t>ЕИС</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="B37" s="14" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Осторожно</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>29.10.2026 07:00</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>Пробирки</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>32616494976</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>Поставка изделий медицинского назначения (пробирки вакуумные)</t>
-        </is>
-      </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>Государственное автономное учреждение Здравоохране</t>
-        </is>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>390420</v>
-      </c>
-      <c r="J37" s="8" t="n">
-        <v>365420</v>
-      </c>
-      <c r="K37" s="8" t="n">
-        <v>-9502</v>
-      </c>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr"/>
-      <c r="N37" s="6" t="inlineStr">
-        <is>
-          <t>Характеристики (объём, размер, гель или без) в ТЗ закрыты (Извещение.zip, часть_II_измененная.docx — zakupki.gov.ru недоступен); среднее НМЦК 13,70 ₽/шт при 15 000 шт «активатор/гель» — если гель, маржа тонкая; ПП 1875: запрет иностранных — нужен российский товар (МиниМед, реестровая запись ПП 719/Г</t>
-        </is>
-      </c>
-      <c r="O37" s="10" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B38" s="14" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Осторожно</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>02.11.2026 10:00</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Одежда/СИЗ/соль</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>0372200087626000024</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Поставка кадетской формы в 2026 году</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>ГБОУ Школа № 380 Красносельского р-на СПб им. А.И.</t>
-        </is>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>2490692</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>2395259</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>-250317</v>
-      </c>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
-      <c r="M38" s="9" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="N38" s="6" t="inlineStr">
-        <is>
-          <t>ПЕРЕСЧИТАНО 27.10: было 33%. Не хватает: ['Подтверждение клиента: правило 3 500 ₽ за китель включает погоны КК, аксельбант, ремень и шеврон или нет (разница 1 848 ₽/шт = 225 тыс. на лот).', 'Подтверждение клиента: шьёт ли он зимнее полупальто (мех. воротник, холлофайбер, съёмный утеплитель) по 5 000</t>
-        </is>
-      </c>
-      <c r="O38" s="10" t="inlineStr">
-        <is>
-          <t>ЕИС</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:O38"/>
+  <autoFilter ref="A3:P36"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O24" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O31" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O33" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O36" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O37" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P33" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P35" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P36" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Участвовать — при опыте 4,85 млн</t>
+          <t>Участвовать (опыт ≥30% НМЦ подтверждён 28.10)</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт ≥ 4,85 млн</t>
+          <t>ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Осторожно — только после КП АРМАТЭК</t>
+          <t>Осторожно — после КП АРМАТЭК (опыт есть)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.372</v>
+        <v>0.362</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         <v>16153216.67</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>10149833</v>
+        <v>10304008</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>6003383.67</v>
+        <v>5849208.67</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>3063717</v>
+        <v>2924051</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
+          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
@@ -1457,11 +1457,11 @@
         <v>12</v>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.144</v>
+        <v>0.141</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Осторожно — после КП АРМАТЭК (опыт есть)</t>
+          <t>Осторожно: КП АРМАТЭК получено, поз. 38 в минусе</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1498,13 +1498,13 @@
         <v>12269140</v>
       </c>
       <c r="K15" s="8" t="n">
-        <v>10507218</v>
+        <v>10535025</v>
       </c>
       <c r="L15" s="8" t="n">
-        <v>1761922</v>
+        <v>1734115</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>-354638</v>
+        <v>-384272</v>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>ПЕРЕСЧИТАНО 27.10: все 83 позиции + доставка; 39% НМЦ — оценка (затворы АРМАТЭК АМ 2,4 млн — цены нет); 16 убыточных строк; при снижении &gt;7% — минус</t>
+          <t>КП 28.10 (АРМАТЭК, ПЭК, ВФЗ, Лидер) учтены; АРМАТЭК поз.38 дороже НМЦ на 40%; ПЕРЕСЧИТАНО 27.10: все 83 позиции + доставка; 39% НМЦ — оценка (затворы АРМАТЭК АМ 2,4 млн — цены нет); 16 убыточных строк; при снижении &gt;7% — минус</t>
         </is>
       </c>
       <c r="Q15" s="10" t="inlineStr">

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.362</v>
+        <v>0.366</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         <v>16153216.67</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>10304008</v>
+        <v>10239786</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5849208.67</v>
+        <v>5913430.67</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>2924051</v>
+        <v>2982228</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
+          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП, ФОБОС ФБ39) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Осторожно: КП АРМАТЭК получено, поз. 38 в минусе</t>
+          <t>Нет — не идём (решение 28.10: только лот 2)</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.366</v>
+        <v>0.355</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         <v>16153216.67</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>10239786</v>
+        <v>10413707</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5913430.67</v>
+        <v>5739509.67</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>2982228</v>
+        <v>2824681</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП, ФОБОС ФБ39) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
+          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП, ФОБОС ФБ39, ЛМЗ 30ч6бр) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.355</v>
+        <v>0.359</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         <v>16153216.67</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>10413707</v>
+        <v>10348193</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5739509.67</v>
+        <v>5805023.67</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>2824681</v>
+        <v>2884027</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП, ФОБОС ФБ39, ЛМЗ 30ч6бр) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
+          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП, ФОБОС ФБ39, ЛМЗ 30ч6бр, Ярдос, Гималаи) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">

--- a/TOP_MARGIN_2710.xlsx
+++ b/TOP_MARGIN_2710.xlsx
@@ -818,7 +818,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.359</v>
+        <v>0.356</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -859,13 +859,13 @@
         <v>16153216.67</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>10348193</v>
+        <v>10398187</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5805023.67</v>
+        <v>5755029.67</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>2884027</v>
+        <v>2838723</v>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП, ФОБОС ФБ39, ЛМЗ 30ч6бр, Ярдос, Гималаи) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
+          <t>КП 28.10 (ПЭК, Доминик, АРМАТЭК ЗИП, ФОБОС ФБ39, ЛМЗ 30ч6бр, Ярдос, Гималаи, АДЛ 30.10) учтены; ПЕРЕСЧИТАНО 27.10: все 87 позиций + контейнер до Южно-Сахалинска; 14% НМЦ — оценка; ~2 млн прибыли даёт п.53 (задвижки Ду500 с ЭП) — нужны КП Авангард/Тулаэлектропривод; опыт есть (подтверждено 28.10); запросы на заводы — SAKHALIN_ZAPROS</t>
         </is>
       </c>
       <c r="Q6" s="10" t="inlineStr">
